--- a/2026/YRIGOYEN 7630/Agosto/YRIGOYEN7630-Agosto.xlsx
+++ b/2026/YRIGOYEN 7630/Agosto/YRIGOYEN7630-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DF6F82-D70A-40AE-9B86-05BDE380C319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F22ED78-57D3-40B9-98F1-61D31145616B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="129">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -359,24 +364,6 @@
     <t>Gastos part</t>
   </si>
   <si>
-    <t>Transf 10/07</t>
-  </si>
-  <si>
-    <t>Debito 02/07</t>
-  </si>
-  <si>
-    <t>Debito 08/07</t>
-  </si>
-  <si>
-    <t>Debito 13/07</t>
-  </si>
-  <si>
-    <t>Debito 16/07</t>
-  </si>
-  <si>
-    <t>Transf 28/07</t>
-  </si>
-  <si>
     <t>VTO 17/09</t>
   </si>
   <si>
@@ -389,19 +376,49 @@
     <t>Sindicatos mes de AGOSTO</t>
   </si>
   <si>
-    <t>Honorarios administracion - Se adeudan $15.000 de JULIO y $165.000 de AGOSTO</t>
-  </si>
-  <si>
-    <t>Nos autodebemos $180.000 para el inicio del mes de agosto (nos falta pagarnos $15.000 de JULIO y $165000 de JULIO)</t>
-  </si>
-  <si>
-    <t>Transf 17/08</t>
-  </si>
-  <si>
     <t>Cuello Natalia - Trabajo cloacal para intentar desobstruir la colectora cloacal</t>
   </si>
   <si>
     <t>Cuello Natalia - Limpieza de columna cocina y baño de todas las UF - Cuota 5/5</t>
+  </si>
+  <si>
+    <t>Debito 04/08</t>
+  </si>
+  <si>
+    <t>Debito 10/08</t>
+  </si>
+  <si>
+    <t>Transf 10/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarios administracion - Se adeuda AGOSTO </t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t>Debito 18/08</t>
+  </si>
+  <si>
+    <t>Transf 18/08</t>
+  </si>
+  <si>
+    <t>Transf 26/08</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Cuota 1/3 -</t>
+  </si>
+  <si>
+    <t>Abonado por Dpto 6</t>
+  </si>
+  <si>
+    <t>Cuota 1/2 -</t>
+  </si>
+  <si>
+    <t>Abonado por Dpto 18</t>
   </si>
 </sst>
 </file>
@@ -418,7 +435,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -614,6 +631,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1112,7 +1136,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1315,9 +1339,6 @@
     </xf>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1382,118 +1403,129 @@
     <xf numFmtId="8" fontId="25" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="26" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1572,9 +1604,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1612,9 +1644,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1647,9 +1679,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1682,9 +1731,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1858,22 +1924,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M121"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="69" t="s">
         <v>54</v>
@@ -1882,7 +1948,7 @@
       <c r="D1" s="69"/>
       <c r="E1" s="70"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="71" t="s">
         <v>28</v>
@@ -1891,16 +1957,16 @@
       <c r="D2" s="71"/>
       <c r="E2" s="72"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="212" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="209"/>
-      <c r="E3" s="210"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="213"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1911,12 +1977,12 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="71" t="s">
@@ -1924,7 +1990,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>90</v>
       </c>
@@ -1935,57 +2001,57 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="212" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="212"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="212"/>
-      <c r="C9" s="212"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="211" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="215" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="215"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="215"/>
+      <c r="C9" s="215"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="215"/>
+      <c r="C10" s="215"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="211"/>
-      <c r="C13" s="211"/>
-      <c r="D13" s="211"/>
-      <c r="E13" s="211"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="211"/>
-      <c r="B14" s="211"/>
-      <c r="C14" s="211"/>
-      <c r="D14" s="211"/>
-      <c r="E14" s="211"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="211"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="211"/>
-      <c r="E15" s="211"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="211"/>
-      <c r="B16" s="211"/>
-      <c r="C16" s="211"/>
-      <c r="D16" s="211"/>
-      <c r="E16" s="211"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="214"/>
+      <c r="C13" s="214"/>
+      <c r="D13" s="214"/>
+      <c r="E13" s="214"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="214"/>
+      <c r="B14" s="214"/>
+      <c r="C14" s="214"/>
+      <c r="D14" s="214"/>
+      <c r="E14" s="214"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="214"/>
+      <c r="B15" s="214"/>
+      <c r="C15" s="214"/>
+      <c r="D15" s="214"/>
+      <c r="E15" s="214"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="214"/>
+      <c r="B16" s="214"/>
+      <c r="C16" s="214"/>
+      <c r="D16" s="214"/>
+      <c r="E16" s="214"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1994,7 +2060,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>34</v>
       </c>
@@ -2003,249 +2069,246 @@
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="191">
-        <v>862885</v>
+      <c r="D22" s="204">
+        <v>851164</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="191"/>
+      <c r="D23" s="190"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="57" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="57"/>
       <c r="C24" s="57"/>
-      <c r="D24" s="192">
+      <c r="D24" s="191">
         <f>SUM(D22:D23)</f>
-        <v>862885</v>
+        <v>851164</v>
       </c>
       <c r="E24" s="138"/>
       <c r="G24" s="22"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="191"/>
+      <c r="D25" s="190"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="191">
+      <c r="D26" s="190">
         <v>0</v>
       </c>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="191">
+      <c r="D27" s="190">
         <v>0</v>
       </c>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="193"/>
+      <c r="D28" s="192"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="57" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="57"/>
       <c r="C29" s="57"/>
-      <c r="D29" s="194">
+      <c r="D29" s="193">
         <f>SUM(D25:D28)</f>
         <v>0</v>
       </c>
       <c r="E29" s="138"/>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B30" s="29"/>
       <c r="C30" s="29"/>
-      <c r="D30" s="195"/>
+      <c r="D30" s="194"/>
       <c r="E30" s="139">
         <f>D24+D29</f>
-        <v>862885</v>
+        <v>851164</v>
       </c>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B31" s="35"/>
       <c r="C31" s="35"/>
-      <c r="D31" s="196"/>
+      <c r="D31" s="195"/>
       <c r="E31" s="140"/>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="207" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" s="208"/>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="210" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="211"/>
       <c r="C32" s="52"/>
-      <c r="D32" s="239">
+      <c r="D32" s="204">
         <v>50000</v>
       </c>
       <c r="E32" s="141"/>
     </row>
-    <row r="33" spans="1:9" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="207" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33" s="208"/>
+    <row r="33" spans="1:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="210" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="211"/>
       <c r="C33" s="52"/>
-      <c r="D33" s="197">
-        <v>150000</v>
+      <c r="D33" s="240">
+        <v>180000</v>
       </c>
       <c r="E33" s="141"/>
-      <c r="G33" s="151" t="s">
+      <c r="G33" s="150" t="s">
         <v>102</v>
       </c>
-      <c r="H33" s="151"/>
-      <c r="I33" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H33" s="150"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="29" t="s">
         <v>16</v>
       </c>
       <c r="B34" s="29"/>
       <c r="C34" s="29"/>
-      <c r="D34" s="198"/>
+      <c r="D34" s="196"/>
       <c r="E34" s="142">
         <f>SUM(D32:D33)</f>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
-      <c r="D35" s="199"/>
+      <c r="D35" s="197"/>
       <c r="E35" s="143"/>
     </row>
-    <row r="36" spans="1:9" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="213" t="s">
+    <row r="36" spans="1:8" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="208" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="214"/>
+      <c r="B36" s="209"/>
       <c r="C36" s="54"/>
-      <c r="D36" s="200">
-        <f>26570+7909</f>
-        <v>34479</v>
-      </c>
-      <c r="E36" s="162" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="207" t="s">
+      <c r="D36" s="237">
+        <f>30025+7909</f>
+        <v>37934</v>
+      </c>
+      <c r="E36" s="161" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="210" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="208"/>
+      <c r="B37" s="211"/>
       <c r="C37" s="54"/>
-      <c r="D37" s="201">
-        <v>54278</v>
-      </c>
-      <c r="E37" s="144" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D37" s="238">
+        <v>69628</v>
+      </c>
+      <c r="E37" s="239" t="str">
+        <f>E36</f>
+        <v>Debito 04/08</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
-      <c r="D38" s="198"/>
-      <c r="E38" s="145">
+      <c r="D38" s="196"/>
+      <c r="E38" s="144">
         <f>SUM(D36:D37)</f>
-        <v>88757</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <v>107562</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="146"/>
-      <c r="C39" s="146"/>
-      <c r="D39" s="202"/>
-      <c r="E39" s="147"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B39" s="145"/>
+      <c r="C39" s="145"/>
+      <c r="D39" s="198"/>
+      <c r="E39" s="146"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="52"/>
-      <c r="D40" s="240">
+      <c r="D40" s="205">
         <v>628219.53</v>
       </c>
-      <c r="E40" s="162" t="s">
-        <v>114</v>
+      <c r="E40" s="161" t="s">
+        <v>117</v>
       </c>
       <c r="G40" s="123"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="52"/>
-      <c r="D41" s="203">
+      <c r="D41" s="205">
         <v>10602.27</v>
       </c>
-      <c r="E41" s="162" t="str">
-        <f>E40</f>
-        <v>Debito 16/07</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E41" s="161" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="52"/>
-      <c r="D42" s="203">
+      <c r="D42" s="205">
         <v>75532.289999999994</v>
       </c>
-      <c r="E42" s="153" t="str">
+      <c r="E42" s="152" t="str">
         <f>E41</f>
-        <v>Debito 16/07</v>
+        <v>Debito 18/08</v>
       </c>
       <c r="F42" s="43">
         <f>D42+D41</f>
@@ -2253,664 +2316,704 @@
       </c>
       <c r="G42" s="137"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="238">
+      <c r="D43" s="203">
         <v>5733.45</v>
       </c>
-      <c r="E43" s="162" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E43" s="161" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="238">
+      <c r="D44" s="203">
         <v>99230.87</v>
       </c>
-      <c r="E44" s="154" t="str">
+      <c r="E44" s="153" t="str">
         <f>E43</f>
-        <v>Debito 13/07</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="238">
+      <c r="D45" s="203">
         <v>51601.05</v>
       </c>
-      <c r="E45" s="155" t="str">
+      <c r="E45" s="154" t="str">
         <f>E44</f>
-        <v>Debito 13/07</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="146"/>
-      <c r="C46" s="146"/>
-      <c r="D46" s="204"/>
-      <c r="E46" s="145">
+      <c r="B46" s="145"/>
+      <c r="C46" s="145"/>
+      <c r="D46" s="199"/>
+      <c r="E46" s="144">
         <f>SUM(D40:D45)</f>
         <v>870919.46000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="146"/>
-      <c r="C47" s="146"/>
-      <c r="D47" s="202"/>
-      <c r="E47" s="147"/>
-    </row>
-    <row r="48" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="145"/>
+      <c r="C47" s="145"/>
+      <c r="D47" s="198"/>
+      <c r="E47" s="146"/>
+    </row>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="156"/>
+      <c r="B48" s="155"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="156">
-        <v>0</v>
-      </c>
-      <c r="E48" s="157"/>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="203">
+        <v>46283.07</v>
+      </c>
+      <c r="E48" s="156"/>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="156"/>
+      <c r="B49" s="155"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="156">
-        <v>0</v>
-      </c>
-      <c r="E49" s="157"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D49" s="155">
+        <v>0</v>
+      </c>
+      <c r="E49" s="156"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="156">
-        <v>41264.699999999997</v>
-      </c>
-      <c r="E50" s="157" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="213" t="s">
+      <c r="D50" s="203">
+        <v>41246.76</v>
+      </c>
+      <c r="E50" s="156" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="214"/>
+      <c r="B51" s="209"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="238">
-        <v>756476.37</v>
-      </c>
-      <c r="E51" s="157" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D51" s="203">
+        <v>530549.97</v>
+      </c>
+      <c r="E51" s="154" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
-      <c r="D52" s="205"/>
-      <c r="E52" s="145">
+      <c r="D52" s="200"/>
+      <c r="E52" s="144">
         <f>SUM(D48:D51)</f>
-        <v>797741.07</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>618079.79999999993</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
         <v>99</v>
       </c>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
-      <c r="D53" s="198"/>
-      <c r="E53" s="148"/>
-    </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="158" t="s">
+      <c r="D53" s="196"/>
+      <c r="E53" s="147"/>
+    </row>
+    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="157" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="152"/>
+      <c r="B54" s="151"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="238">
+      <c r="D54" s="203">
         <v>102500</v>
       </c>
-      <c r="E54" s="157" t="s">
+      <c r="E54" s="156" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="158" t="s">
+    <row r="55" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="157" t="s">
         <v>93</v>
       </c>
-      <c r="B55" s="152"/>
+      <c r="B55" s="151"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="156">
-        <v>0</v>
-      </c>
-      <c r="E55" s="157"/>
-    </row>
-    <row r="56" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="213" t="s">
-        <v>124</v>
-      </c>
-      <c r="B56" s="214"/>
+      <c r="D55" s="155">
+        <v>0</v>
+      </c>
+      <c r="E55" s="156"/>
+    </row>
+    <row r="56" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="243" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="202"/>
       <c r="C56" s="5"/>
       <c r="D56" s="127">
-        <v>333100</v>
-      </c>
-      <c r="E56" s="157" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="213" t="s">
-        <v>123</v>
-      </c>
-      <c r="B57" s="214"/>
+        <f>750000/3</f>
+        <v>250000</v>
+      </c>
+      <c r="E56" s="244" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="243" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="202"/>
       <c r="C57" s="5"/>
       <c r="D57" s="127">
+        <v>60000</v>
+      </c>
+      <c r="E57" s="244" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="157" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="202"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="127">
+        <v>78600</v>
+      </c>
+      <c r="E58" s="156" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="208" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="209"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="127">
+        <v>333100</v>
+      </c>
+      <c r="E59" s="156" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="208" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" s="209"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="127">
         <v>95700</v>
       </c>
-      <c r="E57" s="157" t="s">
+      <c r="E60" s="156" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="29" t="s">
+    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B58" s="35"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="149">
-        <f>SUM(D54:D57)</f>
-        <v>531300</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="35" t="s">
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="148">
+        <f>SUM(D54:D60)</f>
+        <v>919900</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B59" s="67"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="195"/>
-      <c r="E59" s="148"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
+      <c r="B62" s="67"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="194"/>
+      <c r="E62" s="147"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="156">
-        <v>67713</v>
-      </c>
-      <c r="E60" s="150"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="156">
-        <v>70977.45</v>
-      </c>
-      <c r="E61" s="40"/>
-    </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="B62" s="51"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="206"/>
-      <c r="E62" s="103">
-        <f>SUM(D60:D61)</f>
-        <v>138690.45000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="102"/>
-      <c r="E63" s="109"/>
-    </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="30" t="s">
+      <c r="D63" s="155">
+        <v>67713</v>
+      </c>
+      <c r="E63" s="149"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="203">
+        <v>67627.39</v>
+      </c>
+      <c r="E64" s="40"/>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="51"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="201"/>
+      <c r="E65" s="103">
+        <f>SUM(D63:D64)</f>
+        <v>135340.39000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="102"/>
+      <c r="E66" s="109"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="110"/>
-      <c r="E64" s="111">
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="110"/>
+      <c r="E67" s="111">
         <f>4880009.37-4132288.74</f>
         <v>747720.62999999989</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="1"/>
-      <c r="D65" s="112"/>
-      <c r="E65" s="113"/>
-      <c r="F65" s="43"/>
-    </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="D68" s="112"/>
+      <c r="E68" s="113"/>
+      <c r="F68" s="43"/>
+    </row>
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B66" s="10"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="114"/>
-      <c r="E66" s="115">
-        <f>(SUM(E27:E64))</f>
-        <v>4238013.6099999994</v>
-      </c>
-      <c r="F66" s="137">
-        <v>0</v>
-      </c>
-      <c r="G66" s="43"/>
-      <c r="H66" s="123"/>
-      <c r="I66" s="123"/>
-      <c r="J66" s="123"/>
-      <c r="K66" s="123"/>
-      <c r="L66" s="123"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D67" s="112"/>
-      <c r="E67" s="112"/>
-      <c r="H67" s="123"/>
-      <c r="I67" s="123"/>
-      <c r="J67" s="123"/>
-      <c r="K67" s="123"/>
-      <c r="L67" s="123"/>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D68" s="112"/>
-      <c r="E68" s="112"/>
-      <c r="H68" s="161"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
+      <c r="B69" s="10"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="114"/>
+      <c r="E69" s="115">
+        <f>(SUM(E27:E67))</f>
+        <v>4480686.2799999993</v>
+      </c>
+      <c r="F69" s="137">
+        <v>0</v>
+      </c>
+      <c r="G69" s="43"/>
+      <c r="H69" s="123"/>
+      <c r="I69" s="123"/>
+      <c r="J69" s="123"/>
+      <c r="K69" s="123"/>
+      <c r="L69" s="123"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D70" s="112"/>
+      <c r="E70" s="112"/>
+      <c r="H70" s="123"/>
+      <c r="I70" s="123"/>
+      <c r="J70" s="123"/>
+      <c r="K70" s="123"/>
+      <c r="L70" s="123"/>
+    </row>
+    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="112"/>
+      <c r="E71" s="112"/>
+      <c r="H71" s="160"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B69" s="12"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="116"/>
-      <c r="E69" s="117"/>
-    </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="213"/>
-      <c r="B70" s="214"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="127"/>
-      <c r="E70" s="104"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="213"/>
-      <c r="B71" s="214"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="106"/>
-      <c r="E71" s="104"/>
-    </row>
-    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="207"/>
-      <c r="B72" s="208"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="106"/>
-      <c r="E72" s="104"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="105"/>
-      <c r="B73" s="107"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="116"/>
+      <c r="E72" s="117"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="208"/>
+      <c r="B73" s="209"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="106"/>
+      <c r="D73" s="127"/>
       <c r="E73" s="104"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="49"/>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58">
-        <f>SUM(D70:D73)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="30" t="s">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="208"/>
+      <c r="B74" s="209"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="106"/>
+      <c r="E74" s="104"/>
+    </row>
+    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="210"/>
+      <c r="B75" s="211"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="106"/>
+      <c r="E75" s="104"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="105"/>
+      <c r="B76" s="107"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="106"/>
+      <c r="E76" s="104"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="49"/>
+      <c r="B77" s="48"/>
+      <c r="C77" s="48"/>
+      <c r="D77" s="58"/>
+      <c r="E77" s="58">
+        <f>SUM(D73:D76)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="30"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="101"/>
-    </row>
-    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="101"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="10"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="68">
-        <f>E74+E77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="99" t="s">
+      <c r="B82" s="10"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="68">
+        <f>E77+E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B81" s="100">
-        <f>E66</f>
-        <v>4238013.6099999994</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="99" t="s">
+      <c r="B84" s="100">
+        <f>E69</f>
+        <v>4480686.2799999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="B82" s="100">
-        <f>E66-E64</f>
-        <v>3490292.9799999995</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="99" t="s">
+      <c r="B85" s="100">
+        <f>E69-E67</f>
+        <v>3732965.6499999994</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B83" s="100">
-        <f>E79-E77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="99" t="s">
+      <c r="B86" s="100">
+        <f>E82-E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="B84" s="100">
-        <f>E79</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D86" s="123"/>
-      <c r="E86" s="123"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D87" s="123"/>
-      <c r="E87" s="123"/>
-    </row>
-    <row r="88" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="23" t="s">
+      <c r="B87" s="100">
+        <f>E82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D89" s="123"/>
+      <c r="E89" s="123"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D90" s="123"/>
+      <c r="E90" s="123"/>
+    </row>
+    <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B88" s="124"/>
-      <c r="C88" s="24"/>
-    </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="33"/>
-      <c r="B89" s="59">
-        <v>0</v>
-      </c>
-      <c r="C89" s="26"/>
-    </row>
-    <row r="90" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="25" t="s">
+      <c r="B91" s="124"/>
+      <c r="C91" s="24"/>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="33"/>
+      <c r="B92" s="59">
+        <v>0</v>
+      </c>
+      <c r="C92" s="26"/>
+    </row>
+    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B90" s="40">
+      <c r="B93" s="40">
         <f>PRORRATEO!F29</f>
-        <v>4369470.57</v>
-      </c>
-      <c r="C90" s="24"/>
-    </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="25"/>
-      <c r="B91" s="40">
-        <v>0</v>
-      </c>
-      <c r="C91" s="24"/>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="25" t="s">
+        <v>4938034.42</v>
+      </c>
+      <c r="C93" s="24"/>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="25"/>
+      <c r="B94" s="40">
+        <v>0</v>
+      </c>
+      <c r="C94" s="24"/>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B92" s="108">
-        <f>B113</f>
-        <v>0</v>
-      </c>
-      <c r="C92" s="24"/>
-    </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="28"/>
-      <c r="B93" s="47"/>
-      <c r="C93" s="24"/>
-    </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="122" t="s">
+      <c r="B95" s="108">
+        <f>B116</f>
+        <v>0</v>
+      </c>
+      <c r="C95" s="24"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="28"/>
+      <c r="B96" s="47"/>
+      <c r="C96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="B94" s="47"/>
-      <c r="C94" s="24"/>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="39" t="s">
+      <c r="B97" s="47"/>
+      <c r="C97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B95" s="47">
-        <f>-B82</f>
-        <v>-3490292.9799999995</v>
-      </c>
-      <c r="C95" s="24"/>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="28" t="s">
+      <c r="B98" s="47">
+        <f>-B85</f>
+        <v>-3732965.6499999994</v>
+      </c>
+      <c r="C98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B96" s="47">
-        <f>-(B83)</f>
-        <v>0</v>
-      </c>
-      <c r="C96" s="24"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="32" t="s">
+      <c r="B99" s="47">
+        <f>-(B86)</f>
+        <v>0</v>
+      </c>
+      <c r="C99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="59">
-        <f>SUM(B89:B96)</f>
-        <v>879177.59000000078</v>
-      </c>
-      <c r="C97" s="27"/>
-      <c r="D97" s="43"/>
-    </row>
-    <row r="98" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="41"/>
-      <c r="C98" s="27"/>
-      <c r="D98" s="43"/>
-      <c r="E98" s="125"/>
-      <c r="F98" s="126"/>
-    </row>
-    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="42"/>
-      <c r="C99" s="27"/>
-    </row>
-    <row r="100" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100"/>
-      <c r="B100" s="41"/>
-      <c r="C100" s="37"/>
-    </row>
-    <row r="101" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="130" t="s">
+      <c r="B100" s="59">
+        <f>SUM(B92:B99)</f>
+        <v>1205068.7700000005</v>
+      </c>
+      <c r="C100" s="27"/>
+      <c r="D100" s="43"/>
+    </row>
+    <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="41"/>
+      <c r="C101" s="27"/>
+      <c r="D101" s="43"/>
+      <c r="E101" s="125"/>
+      <c r="F101" s="126"/>
+    </row>
+    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="42"/>
+      <c r="C102" s="27"/>
+    </row>
+    <row r="103" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103"/>
+      <c r="B103" s="41"/>
+      <c r="C103" s="37"/>
+    </row>
+    <row r="104" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="B101" s="167">
+      <c r="B104" s="166">
         <v>-2936183.8760999963</v>
       </c>
-      <c r="C101" s="37"/>
-      <c r="D101" s="46"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="54" t="s">
+      <c r="C104" s="37"/>
+      <c r="D104" s="46"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="B102" s="135">
-        <f>-B82</f>
-        <v>-3490292.9799999995</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="54" t="s">
+      <c r="B105" s="135">
+        <f>-B85</f>
+        <v>-3732965.6499999994</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B103" s="135">
-        <f>-B83</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="54" t="s">
+      <c r="B106" s="135">
+        <f>-B86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="B104" s="135">
-        <f>B113</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="54" t="s">
+      <c r="B107" s="135">
+        <f>B116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B105" s="136">
+      <c r="B108" s="136">
         <f>PRORRATEO!F29</f>
-        <v>4369470.57</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="133" t="s">
+        <v>4938034.42</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="B106" s="134">
-        <f>SUM(B101:C105)</f>
-        <v>-2057006.2860999955</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="131"/>
-      <c r="B107" s="131"/>
-    </row>
-    <row r="108" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="216" t="s">
+      <c r="B109" s="134">
+        <f>SUM(B104:C108)</f>
+        <v>-1731115.1060999958</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="131"/>
+      <c r="B110" s="131"/>
+    </row>
+    <row r="111" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="207" t="s">
         <v>32</v>
       </c>
-      <c r="B109" s="216"/>
-      <c r="C109" s="216"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="216"/>
-      <c r="B110" s="216"/>
-      <c r="C110" s="216"/>
-    </row>
-    <row r="111" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="119"/>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36">
+      <c r="B112" s="207"/>
+      <c r="C112" s="207"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="207"/>
+      <c r="B113" s="207"/>
+      <c r="C113" s="207"/>
+    </row>
+    <row r="114" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="119"/>
+      <c r="B114" s="36"/>
+      <c r="C114" s="36">
         <v>40000</v>
       </c>
-      <c r="E111" s="137"/>
-    </row>
-    <row r="112" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="119"/>
-      <c r="B112" s="121"/>
-      <c r="C112" s="118"/>
-      <c r="D112" s="137"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="44" t="s">
+      <c r="E114" s="137"/>
+    </row>
+    <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="119"/>
+      <c r="B115" s="121"/>
+      <c r="C115" s="118"/>
+      <c r="D115" s="137"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B113" s="120">
-        <f>SUM(B111:B112)</f>
-        <v>0</v>
-      </c>
-      <c r="C113" s="45"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M114" s="8"/>
-    </row>
-    <row r="115" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="215"/>
-      <c r="B115" s="215"/>
-      <c r="C115" s="215"/>
-      <c r="D115" s="215"/>
-      <c r="E115" s="215"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="215"/>
-      <c r="B116" s="215"/>
-      <c r="C116" s="215"/>
-      <c r="D116" s="215"/>
-      <c r="E116" s="215"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="215"/>
-      <c r="B117" s="215"/>
-      <c r="C117" s="215"/>
-      <c r="D117" s="215"/>
-      <c r="E117" s="215"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="215"/>
-      <c r="B118" s="215"/>
-      <c r="C118" s="215"/>
-      <c r="D118" s="215"/>
-      <c r="E118" s="215"/>
+      <c r="B116" s="120">
+        <f>SUM(B114:B115)</f>
+        <v>0</v>
+      </c>
+      <c r="C116" s="45"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M117" s="8"/>
+    </row>
+    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="206"/>
+      <c r="B118" s="206"/>
+      <c r="C118" s="206"/>
+      <c r="D118" s="206"/>
+      <c r="E118" s="206"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="206"/>
+      <c r="B119" s="206"/>
+      <c r="C119" s="206"/>
+      <c r="D119" s="206"/>
+      <c r="E119" s="206"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="206"/>
+      <c r="B120" s="206"/>
+      <c r="C120" s="206"/>
+      <c r="D120" s="206"/>
+      <c r="E120" s="206"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="206"/>
+      <c r="B121" s="206"/>
+      <c r="C121" s="206"/>
+      <c r="D121" s="206"/>
+      <c r="E121" s="206"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A115:E118"/>
-    <mergeCell ref="A109:C110"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A56:B56"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A118:E121"/>
+    <mergeCell ref="A112:C113"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A75:B75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2921,45 +3024,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.33203125" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="0.109375" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="0.140625" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="219"/>
-      <c r="M1" s="219"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2967,7 +3070,7 @@
         <v>82</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="159">
+      <c r="F2" s="158">
         <v>86134.56</v>
       </c>
       <c r="G2" s="6"/>
@@ -2986,7 +3089,7 @@
       <c r="O2" s="55"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3003,38 +3106,38 @@
       <c r="N3" s="56"/>
       <c r="O3" s="60"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="224" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="224" t="s">
+      <c r="B4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="224" t="s">
+      <c r="C4" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="216" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="219" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="224" t="s">
+      <c r="F4" s="216" t="s">
         <v>7</v>
       </c>
       <c r="G4" s="226" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="220" t="s">
+      <c r="H4" s="219" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="220" t="s">
+      <c r="I4" s="219" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="220" t="s">
+      <c r="J4" s="219" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="220" t="s">
+      <c r="K4" s="219" t="s">
         <v>109</v>
       </c>
       <c r="L4" s="229" t="s">
@@ -3043,41 +3146,41 @@
       <c r="M4" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="222" t="s">
+      <c r="N4" s="224" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="217" t="s">
+      <c r="O4" s="221" t="s">
         <v>36</v>
       </c>
       <c r="R4" s="129">
         <v>4966143.9300000006</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="225"/>
-      <c r="B5" s="225"/>
-      <c r="C5" s="231"/>
-      <c r="D5" s="225"/>
-      <c r="E5" s="221"/>
-      <c r="F5" s="225"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="218"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="218"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="218"/>
       <c r="G5" s="227"/>
-      <c r="H5" s="221"/>
+      <c r="H5" s="220"/>
       <c r="I5" s="228"/>
-      <c r="J5" s="221"/>
-      <c r="K5" s="221"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
       <c r="L5" s="230"/>
       <c r="M5" s="61" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="N5" s="223"/>
-      <c r="O5" s="218"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="163">
+      <c r="N5" s="225"/>
+      <c r="O5" s="222"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="162">
         <v>1</v>
       </c>
-      <c r="B6" s="163" t="s">
+      <c r="B6" s="162" t="s">
         <v>56</v>
       </c>
       <c r="C6" s="64"/>
@@ -3087,12 +3190,12 @@
       <c r="E6" s="74">
         <v>332235.01</v>
       </c>
-      <c r="F6" s="75">
-        <f t="shared" ref="F6" si="0">E6</f>
+      <c r="F6" s="241">
+        <f>E6</f>
         <v>332235.01</v>
       </c>
       <c r="G6" s="76">
-        <f t="shared" ref="G6:G23" si="1">E6-F6</f>
+        <f t="shared" ref="G6:G23" si="0">E6-F6</f>
         <v>0</v>
       </c>
       <c r="H6" s="76">
@@ -3106,9 +3209,9 @@
         <f>M$2*D6/100</f>
         <v>326472.62685300008</v>
       </c>
-      <c r="K6" s="160"/>
-      <c r="L6" s="160">
-        <f t="shared" ref="L6:L23" si="2">F$2*D6/100</f>
+      <c r="K6" s="159"/>
+      <c r="L6" s="159">
+        <f t="shared" ref="L6:L23" si="1">F$2*D6/100</f>
         <v>5762.4020639999999</v>
       </c>
       <c r="M6" s="80">
@@ -3127,12 +3230,12 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="163">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="162">
         <f>A6+1</f>
         <v>2</v>
       </c>
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="162" t="s">
         <v>57</v>
       </c>
       <c r="C7" s="65"/>
@@ -3140,43 +3243,43 @@
         <v>5.88</v>
       </c>
       <c r="E7" s="74">
-        <v>2411041.02</v>
+        <v>2898882.02</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="76">
-        <f t="shared" si="1"/>
-        <v>2411041.02</v>
+        <f t="shared" si="0"/>
+        <v>2898882.02</v>
       </c>
       <c r="H7" s="76">
-        <f t="shared" ref="H7:H23" si="3">IF(G7&gt;0,G7*3%,0)</f>
-        <v>72331.230599999995</v>
+        <f t="shared" ref="H7:H23" si="2">IF(G7&gt;0,G7*3%,0)</f>
+        <v>86966.460599999991</v>
       </c>
       <c r="I7" s="77">
         <v>0</v>
       </c>
       <c r="J7" s="78">
-        <f t="shared" ref="J7:J23" si="4">M$2*D7%</f>
+        <f t="shared" ref="J7:J23" si="3">M$2*D7%</f>
         <v>286944.55095600005</v>
       </c>
-      <c r="K7" s="160">
+      <c r="K7" s="159">
         <f>24000+99500</f>
         <v>123500</v>
       </c>
-      <c r="L7" s="160">
-        <f t="shared" si="2"/>
+      <c r="L7" s="159">
+        <f t="shared" si="1"/>
         <v>5064.7121280000001</v>
       </c>
       <c r="M7" s="80">
-        <f t="shared" ref="M7:M23" si="5">ROUND(SUM(G7:L7),0) + P7</f>
-        <v>2898882.02</v>
+        <f t="shared" ref="M7:M23" si="4">ROUND(SUM(G7:L7),0) + P7</f>
+        <v>3401358.02</v>
       </c>
       <c r="N7" s="81">
-        <f t="shared" ref="N7:N23" si="6">ROUND(M7*6% + M7,0) + P7</f>
-        <v>3072815.02</v>
+        <f t="shared" ref="N7:N23" si="5">ROUND(M7*6% + M7,0) + P7</f>
+        <v>3605440.02</v>
       </c>
       <c r="O7" s="82">
-        <f t="shared" ref="O7:O23" si="7">ROUND(M7*3%,0) + M7</f>
-        <v>2985848.02</v>
+        <f t="shared" ref="O7:O23" si="6">ROUND(M7*3%,0) + M7</f>
+        <v>3503399.02</v>
       </c>
       <c r="P7" s="43">
         <f>P6+0.01</f>
@@ -3184,67 +3287,67 @@
       </c>
       <c r="Q7" s="43"/>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="163">
-        <f t="shared" ref="A8:A23" si="8">A7+1</f>
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="162">
+        <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
       </c>
-      <c r="B8" s="163" t="s">
+      <c r="B8" s="162" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="164"/>
-      <c r="D8" s="165">
+      <c r="C8" s="163"/>
+      <c r="D8" s="164">
         <v>6.65</v>
       </c>
       <c r="E8" s="75">
-        <v>423888.03</v>
+        <v>560853.03</v>
       </c>
       <c r="F8" s="75">
-        <v>200000.03</v>
+        <v>0</v>
       </c>
       <c r="G8" s="76">
+        <f t="shared" si="0"/>
+        <v>560853.03</v>
+      </c>
+      <c r="H8" s="76">
+        <f t="shared" si="2"/>
+        <v>16825.590899999999</v>
+      </c>
+      <c r="I8" s="77">
+        <v>0</v>
+      </c>
+      <c r="J8" s="78">
+        <f t="shared" si="3"/>
+        <v>324520.62310500006</v>
+      </c>
+      <c r="K8" s="159"/>
+      <c r="L8" s="159">
         <f t="shared" si="1"/>
-        <v>223888.00000000003</v>
-      </c>
-      <c r="H8" s="76">
-        <f t="shared" si="3"/>
-        <v>6716.64</v>
-      </c>
-      <c r="I8" s="77">
-        <v>0</v>
-      </c>
-      <c r="J8" s="78">
+        <v>5727.9482400000006</v>
+      </c>
+      <c r="M8" s="80">
         <f t="shared" si="4"/>
-        <v>324520.62310500006</v>
-      </c>
-      <c r="K8" s="160"/>
-      <c r="L8" s="160">
-        <f t="shared" si="2"/>
-        <v>5727.9482400000006</v>
-      </c>
-      <c r="M8" s="80">
+        <v>907927.03</v>
+      </c>
+      <c r="N8" s="81">
         <f t="shared" si="5"/>
-        <v>560853.03</v>
-      </c>
-      <c r="N8" s="81">
+        <v>962403.03</v>
+      </c>
+      <c r="O8" s="82">
         <f t="shared" si="6"/>
-        <v>594504.03</v>
-      </c>
-      <c r="O8" s="82">
+        <v>935165.03</v>
+      </c>
+      <c r="P8" s="43">
+        <f t="shared" ref="P8:P24" si="8">P7+0.01</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="162">
         <f t="shared" si="7"/>
-        <v>577679.03</v>
-      </c>
-      <c r="P8" s="43">
-        <f t="shared" ref="P8:P24" si="9">P7+0.01</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="163">
-        <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="B9" s="163" t="s">
+      <c r="B9" s="162" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="65"/>
@@ -3254,54 +3357,54 @@
       <c r="E9" s="74">
         <v>334221.03999999998</v>
       </c>
-      <c r="F9" s="75">
-        <f t="shared" ref="F9:F23" si="10">E9</f>
+      <c r="F9" s="241">
+        <f>E9</f>
         <v>334221.03999999998</v>
       </c>
       <c r="G9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="77">
+        <v>0</v>
+      </c>
+      <c r="J9" s="78">
+        <f t="shared" si="3"/>
+        <v>328424.63060100004</v>
+      </c>
+      <c r="K9" s="159"/>
+      <c r="L9" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="77">
-        <v>0</v>
-      </c>
-      <c r="J9" s="78">
+        <v>5796.855888</v>
+      </c>
+      <c r="M9" s="80">
         <f t="shared" si="4"/>
-        <v>328424.63060100004</v>
-      </c>
-      <c r="K9" s="160"/>
-      <c r="L9" s="160">
-        <f t="shared" si="2"/>
-        <v>5796.855888</v>
-      </c>
-      <c r="M9" s="80">
+        <v>334221.03999999998</v>
+      </c>
+      <c r="N9" s="81">
         <f t="shared" si="5"/>
-        <v>334221.03999999998</v>
-      </c>
-      <c r="N9" s="81">
+        <v>354274.04</v>
+      </c>
+      <c r="O9" s="82">
         <f t="shared" si="6"/>
-        <v>354274.04</v>
-      </c>
-      <c r="O9" s="82">
+        <v>344248.04</v>
+      </c>
+      <c r="P9" s="43">
+        <f t="shared" si="8"/>
+        <v>0.04</v>
+      </c>
+      <c r="R9" s="43"/>
+    </row>
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="162">
         <f t="shared" si="7"/>
-        <v>344248.04</v>
-      </c>
-      <c r="P9" s="43">
-        <f t="shared" si="9"/>
-        <v>0.04</v>
-      </c>
-      <c r="R9" s="43"/>
-    </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="163">
-        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="B10" s="163" t="s">
+      <c r="B10" s="162" t="s">
         <v>60</v>
       </c>
       <c r="C10" s="65"/>
@@ -3309,45 +3412,45 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="74">
+        <v>834850.05</v>
+      </c>
+      <c r="F10" s="241">
+        <v>834850.05</v>
+      </c>
+      <c r="G10" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="77">
+        <v>0</v>
+      </c>
+      <c r="J10" s="78">
+        <f t="shared" si="3"/>
+        <v>392352.753348</v>
+      </c>
+      <c r="K10" s="159"/>
+      <c r="L10" s="159">
+        <f t="shared" si="1"/>
+        <v>6925.2186239999983</v>
+      </c>
+      <c r="M10" s="80">
+        <f t="shared" si="4"/>
         <v>399278.05</v>
       </c>
-      <c r="F10" s="75">
-        <v>0</v>
-      </c>
-      <c r="G10" s="76">
-        <f t="shared" si="1"/>
-        <v>399278.05</v>
-      </c>
-      <c r="H10" s="76">
-        <f t="shared" si="3"/>
-        <v>11978.341499999999</v>
-      </c>
-      <c r="I10" s="77">
-        <v>0</v>
-      </c>
-      <c r="J10" s="78">
-        <f t="shared" si="4"/>
-        <v>392352.753348</v>
-      </c>
-      <c r="K10" s="160"/>
-      <c r="L10" s="160">
-        <f t="shared" si="2"/>
-        <v>6925.2186239999983</v>
-      </c>
-      <c r="M10" s="80">
+      <c r="N10" s="81">
         <f t="shared" si="5"/>
-        <v>810534.05</v>
-      </c>
-      <c r="N10" s="81">
+        <v>423235.05</v>
+      </c>
+      <c r="O10" s="82">
         <f t="shared" si="6"/>
-        <v>859166.05</v>
-      </c>
-      <c r="O10" s="82">
-        <f t="shared" si="7"/>
-        <v>834850.05</v>
+        <v>411256.05</v>
       </c>
       <c r="P10" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
       <c r="Q10" t="s">
@@ -3355,12 +3458,12 @@
       </c>
       <c r="R10" s="43"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="163">
-        <f t="shared" si="8"/>
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="162">
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="B11" s="163" t="s">
+      <c r="B11" s="162" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="64"/>
@@ -3370,108 +3473,108 @@
       <c r="E11" s="74">
         <v>234899.06</v>
       </c>
-      <c r="F11" s="75">
-        <f>E11</f>
-        <v>234899.06</v>
+      <c r="F11" s="241">
+        <f>E11+RESUMEN!D56</f>
+        <v>484899.06</v>
       </c>
       <c r="G11" s="76">
+        <f t="shared" si="0"/>
+        <v>-250000</v>
+      </c>
+      <c r="H11" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="77">
+        <v>0</v>
+      </c>
+      <c r="J11" s="78">
+        <f t="shared" si="3"/>
+        <v>230824.44320100005</v>
+      </c>
+      <c r="K11" s="159"/>
+      <c r="L11" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="76">
+        <v>4074.1646880000003</v>
+      </c>
+      <c r="M11" s="80">
+        <f t="shared" si="4"/>
+        <v>-15100.94</v>
+      </c>
+      <c r="N11" s="81">
+        <f t="shared" si="5"/>
+        <v>-16006.94</v>
+      </c>
+      <c r="O11" s="82">
+        <f t="shared" si="6"/>
+        <v>-15553.94</v>
+      </c>
+      <c r="P11" s="43">
+        <f t="shared" si="8"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="179">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="B12" s="179" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="179"/>
+      <c r="D12" s="180">
+        <v>5.67</v>
+      </c>
+      <c r="E12" s="181">
+        <v>1048899.07</v>
+      </c>
+      <c r="F12" s="242">
+        <v>250000</v>
+      </c>
+      <c r="G12" s="183">
+        <f t="shared" si="0"/>
+        <v>798899.07000000007</v>
+      </c>
+      <c r="H12" s="183">
+        <f t="shared" si="2"/>
+        <v>23966.972100000003</v>
+      </c>
+      <c r="I12" s="182">
+        <v>0</v>
+      </c>
+      <c r="J12" s="184">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="77">
-        <v>0</v>
-      </c>
-      <c r="J11" s="78">
+        <v>276696.53127900005</v>
+      </c>
+      <c r="K12" s="185"/>
+      <c r="L12" s="185">
+        <f t="shared" si="1"/>
+        <v>4883.8295519999992</v>
+      </c>
+      <c r="M12" s="186">
         <f t="shared" si="4"/>
-        <v>230824.44320100005</v>
-      </c>
-      <c r="K11" s="160"/>
-      <c r="L11" s="160">
-        <f t="shared" si="2"/>
-        <v>4074.1646880000003</v>
-      </c>
-      <c r="M11" s="80">
+        <v>1104446.07</v>
+      </c>
+      <c r="N12" s="187">
         <f t="shared" si="5"/>
-        <v>234899.06</v>
-      </c>
-      <c r="N11" s="81">
+        <v>1170713.07</v>
+      </c>
+      <c r="O12" s="188">
         <f t="shared" si="6"/>
-        <v>248993.06</v>
-      </c>
-      <c r="O11" s="82">
+        <v>1137579.07</v>
+      </c>
+      <c r="P12" s="43">
+        <f t="shared" si="8"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="162">
         <f t="shared" si="7"/>
-        <v>241946.06</v>
-      </c>
-      <c r="P11" s="43">
-        <f t="shared" si="9"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="180">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="B12" s="180" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="180"/>
-      <c r="D12" s="181">
-        <v>5.67</v>
-      </c>
-      <c r="E12" s="182">
-        <v>994969.07</v>
-      </c>
-      <c r="F12" s="182">
-        <v>250000</v>
-      </c>
-      <c r="G12" s="184">
-        <f t="shared" si="1"/>
-        <v>744969.07</v>
-      </c>
-      <c r="H12" s="184">
-        <f t="shared" si="3"/>
-        <v>22349.072099999998</v>
-      </c>
-      <c r="I12" s="183">
-        <v>0</v>
-      </c>
-      <c r="J12" s="185">
-        <f t="shared" si="4"/>
-        <v>276696.53127900005</v>
-      </c>
-      <c r="K12" s="186"/>
-      <c r="L12" s="186">
-        <f t="shared" si="2"/>
-        <v>4883.8295519999992</v>
-      </c>
-      <c r="M12" s="187">
-        <f t="shared" si="5"/>
-        <v>1048899.07</v>
-      </c>
-      <c r="N12" s="188">
-        <f t="shared" si="6"/>
-        <v>1111833.07</v>
-      </c>
-      <c r="O12" s="189">
-        <f t="shared" si="7"/>
-        <v>1080366.07</v>
-      </c>
-      <c r="P12" s="43">
-        <f t="shared" si="9"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="163">
-        <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="B13" s="163" t="s">
+      <c r="B13" s="162" t="s">
         <v>63</v>
       </c>
       <c r="C13" s="65"/>
@@ -3481,56 +3584,56 @@
       <c r="E13" s="74">
         <v>281580.08</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="241">
         <f>E13</f>
         <v>281580.08</v>
       </c>
       <c r="G13" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="77">
+        <v>0</v>
+      </c>
+      <c r="J13" s="78">
+        <f t="shared" si="3"/>
+        <v>276696.53127900005</v>
+      </c>
+      <c r="K13" s="159"/>
+      <c r="L13" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="77">
-        <v>0</v>
-      </c>
-      <c r="J13" s="78">
+        <v>4883.8295519999992</v>
+      </c>
+      <c r="M13" s="80">
         <f t="shared" si="4"/>
-        <v>276696.53127900005</v>
-      </c>
-      <c r="K13" s="160"/>
-      <c r="L13" s="160">
-        <f t="shared" si="2"/>
-        <v>4883.8295519999992</v>
-      </c>
-      <c r="M13" s="80">
+        <v>281580.08</v>
+      </c>
+      <c r="N13" s="81">
         <f t="shared" si="5"/>
-        <v>281580.08</v>
-      </c>
-      <c r="N13" s="81">
+        <v>298475.08</v>
+      </c>
+      <c r="O13" s="82">
         <f t="shared" si="6"/>
-        <v>298475.08</v>
-      </c>
-      <c r="O13" s="82">
-        <f t="shared" si="7"/>
         <v>290027.08</v>
       </c>
       <c r="P13" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
       <c r="R13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="163">
-        <f t="shared" si="8"/>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="162">
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="B14" s="163" t="s">
+      <c r="B14" s="162" t="s">
         <v>64</v>
       </c>
       <c r="C14" s="65"/>
@@ -3540,53 +3643,53 @@
       <c r="E14" s="74">
         <v>380903.09</v>
       </c>
-      <c r="F14" s="75">
-        <f t="shared" si="10"/>
+      <c r="F14" s="241">
+        <f>E14</f>
         <v>380903.09</v>
       </c>
       <c r="G14" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="77">
+        <v>0</v>
+      </c>
+      <c r="J14" s="78">
+        <f t="shared" si="3"/>
+        <v>374296.7186790001</v>
+      </c>
+      <c r="K14" s="159"/>
+      <c r="L14" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="77">
-        <v>0</v>
-      </c>
-      <c r="J14" s="78">
+        <v>6606.5207519999994</v>
+      </c>
+      <c r="M14" s="80">
         <f t="shared" si="4"/>
-        <v>374296.7186790001</v>
-      </c>
-      <c r="K14" s="160"/>
-      <c r="L14" s="160">
-        <f t="shared" si="2"/>
-        <v>6606.5207519999994</v>
-      </c>
-      <c r="M14" s="80">
+        <v>380903.09</v>
+      </c>
+      <c r="N14" s="81">
         <f t="shared" si="5"/>
-        <v>380903.09</v>
-      </c>
-      <c r="N14" s="81">
+        <v>403757.09</v>
+      </c>
+      <c r="O14" s="82">
         <f t="shared" si="6"/>
-        <v>403757.09</v>
-      </c>
-      <c r="O14" s="82">
+        <v>392330.09</v>
+      </c>
+      <c r="P14" s="43">
+        <f t="shared" si="8"/>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="162">
         <f t="shared" si="7"/>
-        <v>392330.09</v>
-      </c>
-      <c r="P14" s="43">
-        <f t="shared" si="9"/>
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="163">
-        <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="B15" s="163" t="s">
+      <c r="B15" s="162" t="s">
         <v>65</v>
       </c>
       <c r="C15" s="65"/>
@@ -3596,53 +3699,53 @@
       <c r="E15" s="74">
         <v>243341.1</v>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="241">
         <f>E15</f>
         <v>243341.1</v>
       </c>
       <c r="G15" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="77">
+        <v>0</v>
+      </c>
+      <c r="J15" s="78">
+        <f t="shared" si="3"/>
+        <v>239120.45913000006</v>
+      </c>
+      <c r="K15" s="159"/>
+      <c r="L15" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="77">
-        <v>0</v>
-      </c>
-      <c r="J15" s="78">
+        <v>4220.5934400000006</v>
+      </c>
+      <c r="M15" s="80">
         <f t="shared" si="4"/>
-        <v>239120.45913000006</v>
-      </c>
-      <c r="K15" s="160"/>
-      <c r="L15" s="160">
-        <f t="shared" si="2"/>
-        <v>4220.5934400000006</v>
-      </c>
-      <c r="M15" s="80">
+        <v>243341.1</v>
+      </c>
+      <c r="N15" s="81">
         <f t="shared" si="5"/>
-        <v>243341.1</v>
-      </c>
-      <c r="N15" s="81">
+        <v>257942.1</v>
+      </c>
+      <c r="O15" s="82">
         <f t="shared" si="6"/>
-        <v>257942.1</v>
-      </c>
-      <c r="O15" s="82">
+        <v>250641.1</v>
+      </c>
+      <c r="P15" s="43">
+        <f t="shared" si="8"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="162">
         <f t="shared" si="7"/>
-        <v>250641.1</v>
-      </c>
-      <c r="P15" s="43">
-        <f t="shared" si="9"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="163">
-        <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="B16" s="163" t="s">
+      <c r="B16" s="162" t="s">
         <v>66</v>
       </c>
       <c r="C16" s="65"/>
@@ -3650,54 +3753,55 @@
         <v>5.63</v>
       </c>
       <c r="E16" s="74">
+        <v>288234.11</v>
+      </c>
+      <c r="F16" s="241">
+        <f>E16</f>
+        <v>288234.11</v>
+      </c>
+      <c r="G16" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="77">
+        <v>0</v>
+      </c>
+      <c r="J16" s="78">
+        <f t="shared" si="3"/>
+        <v>274744.52753100003</v>
+      </c>
+      <c r="K16" s="159"/>
+      <c r="L16" s="159">
+        <f t="shared" si="1"/>
+        <v>4849.375728</v>
+      </c>
+      <c r="M16" s="80">
+        <f t="shared" si="4"/>
+        <v>279594.11</v>
+      </c>
+      <c r="N16" s="81">
+        <f t="shared" si="5"/>
+        <v>296370.11</v>
+      </c>
+      <c r="O16" s="82">
+        <f t="shared" si="6"/>
         <v>287982.11</v>
       </c>
-      <c r="F16" s="75">
-        <v>279594.11</v>
-      </c>
-      <c r="G16" s="76">
-        <f t="shared" si="1"/>
-        <v>8388</v>
-      </c>
-      <c r="H16" s="76">
-        <f t="shared" si="3"/>
-        <v>251.64</v>
-      </c>
-      <c r="I16" s="77">
-        <v>0</v>
-      </c>
-      <c r="J16" s="78">
-        <f t="shared" si="4"/>
-        <v>274744.52753100003</v>
-      </c>
-      <c r="K16" s="160"/>
-      <c r="L16" s="160">
-        <f t="shared" si="2"/>
-        <v>4849.375728</v>
-      </c>
-      <c r="M16" s="80">
-        <f t="shared" si="5"/>
-        <v>288234.11</v>
-      </c>
-      <c r="N16" s="81">
-        <f t="shared" si="6"/>
-        <v>305528.11</v>
-      </c>
-      <c r="O16" s="82">
+      <c r="P16" s="43">
+        <f t="shared" si="8"/>
+        <v>0.10999999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="162">
         <f t="shared" si="7"/>
-        <v>296881.11</v>
-      </c>
-      <c r="P16" s="43">
-        <f t="shared" si="9"/>
-        <v>0.10999999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="163">
-        <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="B17" s="163" t="s">
+      <c r="B17" s="162" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="65"/>
@@ -3707,53 +3811,53 @@
       <c r="E17" s="74">
         <v>275621.12</v>
       </c>
-      <c r="F17" s="75">
+      <c r="F17" s="241">
         <f>E17</f>
         <v>275621.12</v>
       </c>
       <c r="G17" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="77">
+        <v>0</v>
+      </c>
+      <c r="J17" s="78">
+        <f t="shared" si="3"/>
+        <v>270840.52003500005</v>
+      </c>
+      <c r="K17" s="159"/>
+      <c r="L17" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="77">
-        <v>0</v>
-      </c>
-      <c r="J17" s="78">
+        <v>4780.4680799999996</v>
+      </c>
+      <c r="M17" s="80">
         <f t="shared" si="4"/>
-        <v>270840.52003500005</v>
-      </c>
-      <c r="K17" s="160"/>
-      <c r="L17" s="160">
-        <f t="shared" si="2"/>
-        <v>4780.4680799999996</v>
-      </c>
-      <c r="M17" s="80">
+        <v>275621.12</v>
+      </c>
+      <c r="N17" s="81">
         <f t="shared" si="5"/>
-        <v>275621.12</v>
-      </c>
-      <c r="N17" s="81">
+        <v>292158.12</v>
+      </c>
+      <c r="O17" s="82">
         <f t="shared" si="6"/>
-        <v>292158.12</v>
-      </c>
-      <c r="O17" s="82">
+        <v>283890.12</v>
+      </c>
+      <c r="P17" s="43">
+        <f t="shared" si="8"/>
+        <v>0.11999999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="162">
         <f t="shared" si="7"/>
-        <v>283890.12</v>
-      </c>
-      <c r="P17" s="43">
-        <f t="shared" si="9"/>
-        <v>0.11999999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="163">
-        <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="B18" s="163" t="s">
+      <c r="B18" s="162" t="s">
         <v>68</v>
       </c>
       <c r="C18" s="65"/>
@@ -3763,53 +3867,53 @@
       <c r="E18" s="74">
         <v>549256.13</v>
       </c>
-      <c r="F18" s="75">
-        <f t="shared" si="10"/>
+      <c r="F18" s="241">
+        <f>E18</f>
         <v>549256.13</v>
       </c>
       <c r="G18" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="77">
+        <v>0</v>
+      </c>
+      <c r="J18" s="78">
+        <f t="shared" si="3"/>
+        <v>539729.03632200009</v>
+      </c>
+      <c r="K18" s="159"/>
+      <c r="L18" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="77">
-        <v>0</v>
-      </c>
-      <c r="J18" s="78">
+        <v>9526.4823360000009</v>
+      </c>
+      <c r="M18" s="80">
         <f t="shared" si="4"/>
-        <v>539729.03632200009</v>
-      </c>
-      <c r="K18" s="160"/>
-      <c r="L18" s="160">
-        <f t="shared" si="2"/>
-        <v>9526.4823360000009</v>
-      </c>
-      <c r="M18" s="80">
+        <v>549256.13</v>
+      </c>
+      <c r="N18" s="81">
         <f t="shared" si="5"/>
-        <v>549256.13</v>
-      </c>
-      <c r="N18" s="81">
+        <v>582211.13</v>
+      </c>
+      <c r="O18" s="82">
         <f t="shared" si="6"/>
-        <v>582211.13</v>
-      </c>
-      <c r="O18" s="82">
+        <v>565734.13</v>
+      </c>
+      <c r="P18" s="43">
+        <f t="shared" si="8"/>
+        <v>0.12999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="162">
         <f t="shared" si="7"/>
-        <v>565734.13</v>
-      </c>
-      <c r="P18" s="43">
-        <f t="shared" si="9"/>
-        <v>0.12999999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="163">
-        <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="B19" s="163" t="s">
+      <c r="B19" s="162" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="65"/>
@@ -3817,113 +3921,114 @@
         <v>3.3</v>
       </c>
       <c r="E19" s="74">
-        <v>163883.14000000001</v>
-      </c>
-      <c r="F19" s="75">
-        <v>161040.14000000001</v>
+        <v>166811.14000000001</v>
+      </c>
+      <c r="F19" s="241">
+        <f>1+161040.14</f>
+        <v>161041.14000000001</v>
       </c>
       <c r="G19" s="76">
+        <f t="shared" si="0"/>
+        <v>5770</v>
+      </c>
+      <c r="H19" s="76">
+        <f t="shared" si="2"/>
+        <v>173.1</v>
+      </c>
+      <c r="I19" s="77">
+        <v>0</v>
+      </c>
+      <c r="J19" s="78">
+        <f t="shared" si="3"/>
+        <v>161040.30921000004</v>
+      </c>
+      <c r="K19" s="159"/>
+      <c r="L19" s="159">
         <f t="shared" si="1"/>
-        <v>2843</v>
-      </c>
-      <c r="H19" s="76">
-        <f t="shared" si="3"/>
-        <v>85.289999999999992</v>
-      </c>
-      <c r="I19" s="77">
-        <v>0</v>
-      </c>
-      <c r="J19" s="78">
+        <v>2842.4404799999993</v>
+      </c>
+      <c r="M19" s="80">
         <f t="shared" si="4"/>
-        <v>161040.30921000004</v>
-      </c>
-      <c r="K19" s="160"/>
-      <c r="L19" s="160">
-        <f t="shared" si="2"/>
-        <v>2842.4404799999993</v>
-      </c>
-      <c r="M19" s="80">
+        <v>169826.14</v>
+      </c>
+      <c r="N19" s="81">
         <f t="shared" si="5"/>
-        <v>166811.14000000001</v>
-      </c>
-      <c r="N19" s="81">
+        <v>180016.14</v>
+      </c>
+      <c r="O19" s="82">
         <f t="shared" si="6"/>
-        <v>176820.14</v>
-      </c>
-      <c r="O19" s="82">
-        <f t="shared" si="7"/>
-        <v>171815.14</v>
+        <v>174921.14</v>
       </c>
       <c r="P19" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="Q19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="163">
-        <f t="shared" si="8"/>
+    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="162">
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="B20" s="163" t="s">
+      <c r="B20" s="162" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="164"/>
-      <c r="D20" s="165">
+      <c r="C20" s="163"/>
+      <c r="D20" s="164">
         <v>1.8</v>
       </c>
       <c r="E20" s="75">
         <v>89391.15</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="241">
         <f>E20</f>
         <v>89391.15</v>
       </c>
       <c r="G20" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="77">
+        <v>0</v>
+      </c>
+      <c r="J20" s="78">
+        <f t="shared" si="3"/>
+        <v>87840.168660000025</v>
+      </c>
+      <c r="K20" s="159"/>
+      <c r="L20" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="77">
-        <v>0</v>
-      </c>
-      <c r="J20" s="78">
+        <v>1550.4220800000001</v>
+      </c>
+      <c r="M20" s="80">
         <f t="shared" si="4"/>
-        <v>87840.168660000025</v>
-      </c>
-      <c r="K20" s="160"/>
-      <c r="L20" s="160">
-        <f t="shared" si="2"/>
-        <v>1550.4220800000001</v>
-      </c>
-      <c r="M20" s="80">
+        <v>89391.15</v>
+      </c>
+      <c r="N20" s="81">
         <f t="shared" si="5"/>
-        <v>89391.15</v>
-      </c>
-      <c r="N20" s="81">
+        <v>94755.15</v>
+      </c>
+      <c r="O20" s="82">
         <f t="shared" si="6"/>
-        <v>94755.15</v>
-      </c>
-      <c r="O20" s="82">
-        <f t="shared" si="7"/>
         <v>92073.15</v>
       </c>
       <c r="P20" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
       <c r="Q20" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="B21" s="64" t="s">
@@ -3936,55 +4041,55 @@
       <c r="E21" s="74">
         <v>159910.16</v>
       </c>
-      <c r="F21" s="75">
-        <f t="shared" si="10"/>
+      <c r="F21" s="241">
+        <f t="shared" ref="F9:F23" si="9">E21</f>
         <v>159910.16</v>
       </c>
       <c r="G21" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="77">
+        <v>0</v>
+      </c>
+      <c r="J21" s="78">
+        <f t="shared" si="3"/>
+        <v>157136.30171400003</v>
+      </c>
+      <c r="K21" s="159"/>
+      <c r="L21" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="77">
-        <v>0</v>
-      </c>
-      <c r="J21" s="78">
+        <v>2773.5328319999999</v>
+      </c>
+      <c r="M21" s="80">
         <f t="shared" si="4"/>
-        <v>157136.30171400003</v>
-      </c>
-      <c r="K21" s="160"/>
-      <c r="L21" s="160">
-        <f t="shared" si="2"/>
-        <v>2773.5328319999999</v>
-      </c>
-      <c r="M21" s="80">
+        <v>159910.16</v>
+      </c>
+      <c r="N21" s="81">
         <f t="shared" si="5"/>
-        <v>159910.16</v>
-      </c>
-      <c r="N21" s="81">
+        <v>169505.16</v>
+      </c>
+      <c r="O21" s="82">
         <f t="shared" si="6"/>
-        <v>169505.16</v>
-      </c>
-      <c r="O21" s="82">
+        <v>164707.16</v>
+      </c>
+      <c r="P21" s="43">
+        <f t="shared" si="8"/>
+        <v>0.16</v>
+      </c>
+      <c r="Q21" s="123"/>
+      <c r="R21" s="165"/>
+      <c r="S21" s="165"/>
+      <c r="T21" s="165"/>
+      <c r="U21" s="165"/>
+    </row>
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="64">
         <f t="shared" si="7"/>
-        <v>164707.16</v>
-      </c>
-      <c r="P21" s="43">
-        <f t="shared" si="9"/>
-        <v>0.16</v>
-      </c>
-      <c r="Q21" s="123"/>
-      <c r="R21" s="166"/>
-      <c r="S21" s="166"/>
-      <c r="T21" s="166"/>
-      <c r="U21" s="166"/>
-    </row>
-    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="64">
-        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="B22" s="64" t="s">
@@ -3995,59 +4100,58 @@
         <v>2.61</v>
       </c>
       <c r="E22" s="75">
-        <v>384927.17</v>
+        <v>129616.17</v>
       </c>
       <c r="F22" s="75">
-        <f>E22</f>
-        <v>384927.17</v>
+        <v>0</v>
       </c>
       <c r="G22" s="76">
+        <f t="shared" si="0"/>
+        <v>129616.17</v>
+      </c>
+      <c r="H22" s="76">
+        <f t="shared" si="2"/>
+        <v>3888.4850999999999</v>
+      </c>
+      <c r="I22" s="77">
+        <v>0</v>
+      </c>
+      <c r="J22" s="78">
+        <f t="shared" si="3"/>
+        <v>127368.24455700001</v>
+      </c>
+      <c r="K22" s="159"/>
+      <c r="L22" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="77">
-        <v>0</v>
-      </c>
-      <c r="J22" s="78">
+        <v>2248.1120159999996</v>
+      </c>
+      <c r="M22" s="80">
         <f t="shared" si="4"/>
-        <v>127368.24455700001</v>
-      </c>
-      <c r="K22" s="160"/>
-      <c r="L22" s="160">
-        <f t="shared" si="2"/>
-        <v>2248.1120159999996</v>
-      </c>
-      <c r="M22" s="80">
+        <v>263121.17</v>
+      </c>
+      <c r="N22" s="81">
         <f t="shared" si="5"/>
-        <v>129616.17</v>
-      </c>
-      <c r="N22" s="81">
+        <v>278908.17</v>
+      </c>
+      <c r="O22" s="82">
         <f t="shared" si="6"/>
-        <v>137393.17000000001</v>
-      </c>
-      <c r="O22" s="82">
-        <f t="shared" si="7"/>
-        <v>133504.16999999998</v>
+        <v>271015.17</v>
       </c>
       <c r="P22" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
       <c r="Q22" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="R22" s="166"/>
-      <c r="S22" s="166"/>
-      <c r="T22" s="166"/>
-      <c r="U22" s="166"/>
-    </row>
-    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R22" s="165"/>
+      <c r="S22" s="165"/>
+      <c r="T22" s="165"/>
+      <c r="U22" s="165"/>
+    </row>
+    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="B23" s="64" t="s">
@@ -4060,74 +4164,74 @@
       <c r="E23" s="74">
         <v>212551.18</v>
       </c>
-      <c r="F23" s="75">
-        <f t="shared" si="10"/>
-        <v>212551.18</v>
+      <c r="F23" s="241">
+        <f>E23+RESUMEN!D57</f>
+        <v>272551.18</v>
       </c>
       <c r="G23" s="76">
+        <f t="shared" si="0"/>
+        <v>-60000</v>
+      </c>
+      <c r="H23" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="77">
+        <v>0</v>
+      </c>
+      <c r="J23" s="78">
+        <f t="shared" si="3"/>
+        <v>208864.40103600005</v>
+      </c>
+      <c r="K23" s="159"/>
+      <c r="L23" s="159">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="77">
-        <v>0</v>
-      </c>
-      <c r="J23" s="78">
+        <v>3686.5591680000002</v>
+      </c>
+      <c r="M23" s="80">
         <f t="shared" si="4"/>
-        <v>208864.40103600005</v>
-      </c>
-      <c r="K23" s="160"/>
-      <c r="L23" s="160">
-        <f t="shared" si="2"/>
-        <v>3686.5591680000002</v>
-      </c>
-      <c r="M23" s="80">
+        <v>152551.18</v>
+      </c>
+      <c r="N23" s="81">
         <f t="shared" si="5"/>
-        <v>212551.18</v>
-      </c>
-      <c r="N23" s="81">
+        <v>161704.18</v>
+      </c>
+      <c r="O23" s="82">
         <f t="shared" si="6"/>
-        <v>225304.18</v>
-      </c>
-      <c r="O23" s="82">
-        <f t="shared" si="7"/>
-        <v>218928.18</v>
+        <v>157128.18</v>
       </c>
       <c r="P23" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="Q23" s="166"/>
-      <c r="R23" s="166"/>
-      <c r="S23" s="166"/>
-      <c r="T23" s="166"/>
-      <c r="U23" s="166"/>
-    </row>
-    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q23" s="165"/>
+      <c r="R23" s="165"/>
+      <c r="S23" s="165"/>
+      <c r="T23" s="165"/>
+      <c r="U23" s="165"/>
+    </row>
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="64"/>
       <c r="B24" s="64"/>
       <c r="C24" s="65"/>
       <c r="D24" s="73"/>
       <c r="E24" s="74"/>
-      <c r="F24" s="190"/>
+      <c r="F24" s="189"/>
       <c r="G24" s="76"/>
       <c r="H24" s="76"/>
       <c r="I24" s="77"/>
       <c r="J24" s="78"/>
-      <c r="K24" s="160"/>
+      <c r="K24" s="159"/>
       <c r="L24" s="79"/>
       <c r="M24" s="80"/>
       <c r="N24" s="81"/>
       <c r="O24" s="82"/>
       <c r="P24" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="83"/>
       <c r="B25" s="64"/>
       <c r="C25" s="65"/>
@@ -4138,14 +4242,14 @@
       <c r="H25" s="76"/>
       <c r="I25" s="77"/>
       <c r="J25" s="88"/>
-      <c r="K25" s="179"/>
+      <c r="K25" s="178"/>
       <c r="L25" s="89"/>
       <c r="M25" s="80"/>
       <c r="N25" s="81"/>
       <c r="O25" s="82"/>
       <c r="P25" s="43"/>
     </row>
-    <row r="26" spans="1:21" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="83"/>
       <c r="B26" s="66"/>
       <c r="C26" s="65"/>
@@ -4156,14 +4260,14 @@
       <c r="H26" s="76"/>
       <c r="I26" s="77"/>
       <c r="J26" s="88"/>
-      <c r="K26" s="179"/>
+      <c r="K26" s="178"/>
       <c r="L26" s="89"/>
       <c r="M26" s="80"/>
       <c r="N26" s="81"/>
       <c r="O26" s="82"/>
       <c r="P26" s="43"/>
     </row>
-    <row r="27" spans="1:21" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="84"/>
       <c r="B27" s="64"/>
       <c r="C27" s="65"/>
@@ -4174,14 +4278,14 @@
       <c r="H27" s="76"/>
       <c r="I27" s="77"/>
       <c r="J27" s="88"/>
-      <c r="K27" s="179"/>
+      <c r="K27" s="178"/>
       <c r="L27" s="89"/>
       <c r="M27" s="80"/>
       <c r="N27" s="81"/>
       <c r="O27" s="82"/>
       <c r="P27" s="43"/>
     </row>
-    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="64"/>
       <c r="B28" s="90"/>
       <c r="C28" s="90"/>
@@ -4192,14 +4296,14 @@
       <c r="H28" s="76"/>
       <c r="I28" s="77"/>
       <c r="J28" s="88"/>
-      <c r="K28" s="179"/>
+      <c r="K28" s="178"/>
       <c r="L28" s="89"/>
       <c r="M28" s="91"/>
       <c r="N28" s="92"/>
       <c r="O28" s="93"/>
       <c r="P28" s="43"/>
     </row>
-    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="94"/>
       <c r="B29" s="95"/>
       <c r="C29" s="95"/>
@@ -4209,146 +4313,140 @@
       </c>
       <c r="E29" s="53">
         <f>SUM(E6:E28)</f>
-        <v>8159877.71</v>
+        <v>9022054.7100000009</v>
       </c>
       <c r="F29" s="62">
         <f>SUM(F6:F28)</f>
-        <v>4369470.57</v>
+        <v>4938034.42</v>
       </c>
       <c r="G29" s="62">
         <f>SUM(G6:G28)</f>
-        <v>3790407.1399999997</v>
+        <v>4084020.29</v>
       </c>
       <c r="H29" s="62">
-        <f t="shared" ref="H29:N29" si="11">SUM(H6:H28)</f>
-        <v>113712.21419999999</v>
+        <f t="shared" ref="H29:N29" si="10">SUM(H6:H28)</f>
+        <v>131820.60869999998</v>
       </c>
       <c r="I29" s="62">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J29" s="132">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4883913.3774960004</v>
       </c>
       <c r="K29" s="132"/>
       <c r="L29" s="62">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>86203.467647999991</v>
       </c>
       <c r="M29" s="97">
         <f>SUM(M6:M23)</f>
-        <v>8997738.7100000009</v>
+        <v>9309459.7100000009</v>
       </c>
       <c r="N29" s="97">
-        <f t="shared" si="11"/>
-        <v>9537603.7100000009</v>
+        <f t="shared" si="10"/>
+        <v>9868029.7100000009</v>
       </c>
       <c r="O29" s="97">
         <f>SUM(O6:O28)</f>
-        <v>9267670.7100000009</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9588744.7100000009</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="50"/>
       <c r="C30" s="50"/>
     </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="215" t="str">
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="206" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="215"/>
-      <c r="D32" s="215"/>
-      <c r="E32" s="215"/>
-      <c r="F32" s="215"/>
-      <c r="G32" s="215"/>
-      <c r="H32" s="215"/>
-      <c r="I32" s="215"/>
-      <c r="J32" s="215"/>
-      <c r="K32" s="215"/>
-      <c r="L32" s="215"/>
-      <c r="M32" s="215"/>
-    </row>
-    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="215"/>
-      <c r="C33" s="215"/>
-      <c r="D33" s="215"/>
-      <c r="E33" s="215"/>
-      <c r="F33" s="215"/>
-      <c r="G33" s="215"/>
-      <c r="H33" s="215"/>
-      <c r="I33" s="215"/>
-      <c r="J33" s="215"/>
-      <c r="K33" s="215"/>
-      <c r="L33" s="215"/>
-      <c r="M33" s="215"/>
-    </row>
-    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="215"/>
-      <c r="C34" s="215"/>
-      <c r="D34" s="215"/>
-      <c r="E34" s="215"/>
-      <c r="F34" s="215"/>
-      <c r="G34" s="215"/>
-      <c r="H34" s="215"/>
-      <c r="I34" s="215"/>
-      <c r="J34" s="215"/>
-      <c r="K34" s="215"/>
-      <c r="L34" s="215"/>
-      <c r="M34" s="215"/>
-    </row>
-    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="215"/>
-      <c r="C35" s="215"/>
-      <c r="D35" s="215"/>
-      <c r="E35" s="215"/>
-      <c r="F35" s="215"/>
-      <c r="G35" s="215"/>
-      <c r="H35" s="215"/>
-      <c r="I35" s="215"/>
-      <c r="J35" s="215"/>
-      <c r="K35" s="215"/>
-      <c r="L35" s="215"/>
-      <c r="M35" s="215"/>
-    </row>
-    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="215"/>
-      <c r="C36" s="215"/>
-      <c r="D36" s="215"/>
-      <c r="E36" s="215"/>
-      <c r="F36" s="215"/>
-      <c r="G36" s="215"/>
-      <c r="H36" s="215"/>
-      <c r="I36" s="215"/>
-      <c r="J36" s="215"/>
-      <c r="K36" s="215"/>
-      <c r="L36" s="215"/>
-      <c r="M36" s="215"/>
-    </row>
-    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="215"/>
-      <c r="C37" s="215"/>
-      <c r="D37" s="215"/>
-      <c r="E37" s="215"/>
-      <c r="F37" s="215"/>
-      <c r="G37" s="215"/>
-      <c r="H37" s="215"/>
-      <c r="I37" s="215"/>
-      <c r="J37" s="215"/>
-      <c r="K37" s="215"/>
-      <c r="L37" s="215"/>
-      <c r="M37" s="215"/>
+      <c r="C32" s="206"/>
+      <c r="D32" s="206"/>
+      <c r="E32" s="206"/>
+      <c r="F32" s="206"/>
+      <c r="G32" s="206"/>
+      <c r="H32" s="206"/>
+      <c r="I32" s="206"/>
+      <c r="J32" s="206"/>
+      <c r="K32" s="206"/>
+      <c r="L32" s="206"/>
+      <c r="M32" s="206"/>
+    </row>
+    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="206"/>
+      <c r="C33" s="206"/>
+      <c r="D33" s="206"/>
+      <c r="E33" s="206"/>
+      <c r="F33" s="206"/>
+      <c r="G33" s="206"/>
+      <c r="H33" s="206"/>
+      <c r="I33" s="206"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="206"/>
+      <c r="L33" s="206"/>
+      <c r="M33" s="206"/>
+    </row>
+    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="206"/>
+      <c r="C34" s="206"/>
+      <c r="D34" s="206"/>
+      <c r="E34" s="206"/>
+      <c r="F34" s="206"/>
+      <c r="G34" s="206"/>
+      <c r="H34" s="206"/>
+      <c r="I34" s="206"/>
+      <c r="J34" s="206"/>
+      <c r="K34" s="206"/>
+      <c r="L34" s="206"/>
+      <c r="M34" s="206"/>
+    </row>
+    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="206"/>
+      <c r="C35" s="206"/>
+      <c r="D35" s="206"/>
+      <c r="E35" s="206"/>
+      <c r="F35" s="206"/>
+      <c r="G35" s="206"/>
+      <c r="H35" s="206"/>
+      <c r="I35" s="206"/>
+      <c r="J35" s="206"/>
+      <c r="K35" s="206"/>
+      <c r="L35" s="206"/>
+      <c r="M35" s="206"/>
+    </row>
+    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="206"/>
+      <c r="C36" s="206"/>
+      <c r="D36" s="206"/>
+      <c r="E36" s="206"/>
+      <c r="F36" s="206"/>
+      <c r="G36" s="206"/>
+      <c r="H36" s="206"/>
+      <c r="I36" s="206"/>
+      <c r="J36" s="206"/>
+      <c r="K36" s="206"/>
+      <c r="L36" s="206"/>
+      <c r="M36" s="206"/>
+    </row>
+    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="206"/>
+      <c r="C37" s="206"/>
+      <c r="D37" s="206"/>
+      <c r="E37" s="206"/>
+      <c r="F37" s="206"/>
+      <c r="G37" s="206"/>
+      <c r="H37" s="206"/>
+      <c r="I37" s="206"/>
+      <c r="J37" s="206"/>
+      <c r="K37" s="206"/>
+      <c r="L37" s="206"/>
+      <c r="M37" s="206"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B32:M37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="H4:H5"/>
@@ -4359,6 +4457,12 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4368,142 +4472,142 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="171" t="s">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="170" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="172">
+      <c r="C2" s="171">
         <v>1</v>
       </c>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168"/>
-      <c r="F2" s="169"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="173" t="s">
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="168"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="172" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="174" t="s">
+      <c r="C3" s="173" t="s">
         <v>105</v>
       </c>
-      <c r="F3" s="170"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="232" t="s">
+      <c r="F3" s="169"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="231" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="233"/>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="234"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="232"/>
-      <c r="C5" s="233"/>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="234"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C4" s="232"/>
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="233"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="231"/>
+      <c r="C5" s="232"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="233"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="123"/>
-      <c r="B6" s="232"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="233"/>
-      <c r="E6" s="233"/>
-      <c r="F6" s="234"/>
+      <c r="B6" s="231"/>
+      <c r="C6" s="232"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="233"/>
       <c r="N6" s="123"/>
       <c r="O6" s="123"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="123"/>
-      <c r="B7" s="232"/>
-      <c r="C7" s="233"/>
-      <c r="D7" s="233"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="234"/>
+      <c r="B7" s="231"/>
+      <c r="C7" s="232"/>
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="233"/>
       <c r="N7" s="123"/>
       <c r="O7" s="123"/>
     </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="123"/>
-      <c r="B8" s="235"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="236"/>
-      <c r="E8" s="236"/>
-      <c r="F8" s="237"/>
+      <c r="B8" s="234"/>
+      <c r="C8" s="235"/>
+      <c r="D8" s="235"/>
+      <c r="E8" s="235"/>
+      <c r="F8" s="236"/>
       <c r="N8" s="123"/>
       <c r="O8" s="123"/>
     </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="123"/>
       <c r="N9" s="123"/>
       <c r="O9" s="123"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="123"/>
-      <c r="B10" s="175" t="s">
+      <c r="B10" s="174" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="176">
+      <c r="C10" s="175">
         <v>1</v>
       </c>
-      <c r="D10" s="168"/>
-      <c r="E10" s="168"/>
-      <c r="F10" s="169"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="168"/>
       <c r="N10" s="123"/>
       <c r="O10" s="123"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="123"/>
-      <c r="B11" s="177" t="s">
+      <c r="B11" s="176" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="178" t="s">
+      <c r="C11" s="177" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="170"/>
+      <c r="F11" s="169"/>
       <c r="N11" s="123"/>
       <c r="O11" s="123"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="232" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="233"/>
-      <c r="D12" s="233"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="234"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="232"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="233"/>
-      <c r="E13" s="233"/>
-      <c r="F13" s="234"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="232"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="234"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="232"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="233"/>
-      <c r="E15" s="233"/>
-      <c r="F15" s="234"/>
-    </row>
-    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="235"/>
-      <c r="C16" s="236"/>
-      <c r="D16" s="236"/>
-      <c r="E16" s="236"/>
-      <c r="F16" s="237"/>
+      <c r="C12" s="232"/>
+      <c r="D12" s="232"/>
+      <c r="E12" s="232"/>
+      <c r="F12" s="233"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="231"/>
+      <c r="C13" s="232"/>
+      <c r="D13" s="232"/>
+      <c r="E13" s="232"/>
+      <c r="F13" s="233"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="231"/>
+      <c r="C14" s="232"/>
+      <c r="D14" s="232"/>
+      <c r="E14" s="232"/>
+      <c r="F14" s="233"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="231"/>
+      <c r="C15" s="232"/>
+      <c r="D15" s="232"/>
+      <c r="E15" s="232"/>
+      <c r="F15" s="233"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="234"/>
+      <c r="C16" s="235"/>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="236"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/YRIGOYEN 7630/Agosto/YRIGOYEN7630-Agosto.xlsx
+++ b/2026/YRIGOYEN 7630/Agosto/YRIGOYEN7630-Agosto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F22ED78-57D3-40B9-98F1-61D31145616B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D139AC-06F0-4929-A388-AB7CA9E107F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -409,16 +409,16 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Cuota 1/3 -</t>
-  </si>
-  <si>
     <t>Abonado por Dpto 6</t>
   </si>
   <si>
-    <t>Cuota 1/2 -</t>
-  </si>
-  <si>
     <t>Abonado por Dpto 18</t>
+  </si>
+  <si>
+    <t>Cuota 1/3 - Pintura dpto 6 - Material y mano de obra</t>
+  </si>
+  <si>
+    <t>Cuota 1/2 - Mamposteria, arreglo administracion anterior</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,13 +631,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1136,7 +1129,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1146,7 +1139,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1414,9 +1406,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1510,22 +1514,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="16" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="26" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1940,134 +1928,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="15"/>
-      <c r="B1" s="69" t="s">
+      <c r="A1" s="14"/>
+      <c r="B1" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="70"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="71" t="s">
+      <c r="A2" s="15"/>
+      <c r="B2" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="72"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="71"/>
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="212" t="s">
+      <c r="A3" s="15"/>
+      <c r="B3" s="215" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="213"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="216"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="98" t="s">
+      <c r="A4" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="71" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="18"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="215" t="s">
+      <c r="B8" s="218" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="215"/>
+      <c r="C8" s="218"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="215"/>
-      <c r="C9" s="215"/>
+      <c r="B9" s="218"/>
+      <c r="C9" s="218"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="215"/>
-      <c r="C10" s="215"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="214" t="s">
+      <c r="A13" s="217" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="214"/>
-      <c r="C13" s="214"/>
-      <c r="D13" s="214"/>
-      <c r="E13" s="214"/>
+      <c r="B13" s="217"/>
+      <c r="C13" s="217"/>
+      <c r="D13" s="217"/>
+      <c r="E13" s="217"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="214"/>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
-      <c r="D14" s="214"/>
-      <c r="E14" s="214"/>
+      <c r="A14" s="217"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="217"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="214"/>
-      <c r="B15" s="214"/>
-      <c r="C15" s="214"/>
-      <c r="D15" s="214"/>
-      <c r="E15" s="214"/>
+      <c r="A15" s="217"/>
+      <c r="B15" s="217"/>
+      <c r="C15" s="217"/>
+      <c r="D15" s="217"/>
+      <c r="E15" s="217"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="214"/>
-      <c r="B16" s="214"/>
-      <c r="C16" s="214"/>
-      <c r="D16" s="214"/>
-      <c r="E16" s="214"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A16" s="217"/>
+      <c r="B16" s="217"/>
+      <c r="C16" s="217"/>
+      <c r="D16" s="217"/>
+      <c r="E16" s="217"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="111"/>
+    </row>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="D18" s="111"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="111"/>
+    </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="14"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
@@ -2075,7 +2068,7 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="204">
+      <c r="D22" s="189">
         <v>851164</v>
       </c>
       <c r="E22" s="5"/>
@@ -2084,21 +2077,21 @@
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="190"/>
+      <c r="D23" s="189"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="191">
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="190">
         <f>SUM(D22:D23)</f>
         <v>851164</v>
       </c>
-      <c r="E24" s="138"/>
-      <c r="G24" s="22"/>
+      <c r="E24" s="137"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -2106,7 +2099,7 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="190"/>
+      <c r="D25" s="189"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2115,7 +2108,7 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="190">
+      <c r="D26" s="189">
         <v>0</v>
       </c>
       <c r="E26" s="5"/>
@@ -2126,7 +2119,7 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="190">
+      <c r="D27" s="189">
         <v>0</v>
       </c>
       <c r="E27" s="5"/>
@@ -2137,163 +2130,163 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="192"/>
+      <c r="D28" s="191"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="193">
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="192">
         <f>SUM(D25:D28)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="138"/>
+      <c r="E29" s="137"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="194"/>
-      <c r="E30" s="139">
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="193"/>
+      <c r="E30" s="138">
         <f>D24+D29</f>
         <v>851164</v>
       </c>
-      <c r="F30" s="22"/>
+      <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="195"/>
-      <c r="E31" s="140"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="194"/>
+      <c r="E31" s="139"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="210" t="s">
+      <c r="A32" s="213" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="211"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="204">
+      <c r="B32" s="214"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="189">
         <v>50000</v>
       </c>
-      <c r="E32" s="141"/>
+      <c r="E32" s="140"/>
     </row>
     <row r="33" spans="1:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="210" t="s">
+      <c r="A33" s="213" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="211"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="240">
+      <c r="B33" s="214"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="204">
         <v>180000</v>
       </c>
-      <c r="E33" s="141"/>
-      <c r="G33" s="150" t="s">
+      <c r="E33" s="140"/>
+      <c r="G33" s="149" t="s">
         <v>102</v>
       </c>
-      <c r="H33" s="150"/>
+      <c r="H33" s="149"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="196"/>
-      <c r="E34" s="142">
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="195"/>
+      <c r="E34" s="141">
         <f>SUM(D32:D33)</f>
         <v>230000</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
+      <c r="A35" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="197"/>
-      <c r="E35" s="143"/>
-    </row>
-    <row r="36" spans="1:8" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="208" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="196"/>
+      <c r="E35" s="142"/>
+    </row>
+    <row r="36" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="211" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="209"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="237">
+      <c r="B36" s="212"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="205">
         <f>30025+7909</f>
         <v>37934</v>
       </c>
-      <c r="E36" s="161" t="s">
+      <c r="E36" s="160" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="210" t="s">
+      <c r="A37" s="213" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="211"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="238">
+      <c r="B37" s="214"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="206">
         <v>69628</v>
       </c>
-      <c r="E37" s="239" t="str">
+      <c r="E37" s="202" t="str">
         <f>E36</f>
         <v>Debito 04/08</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="196"/>
-      <c r="E38" s="144">
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="195"/>
+      <c r="E38" s="143">
         <f>SUM(D36:D37)</f>
         <v>107562</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="145"/>
-      <c r="C39" s="145"/>
-      <c r="D39" s="198"/>
-      <c r="E39" s="146"/>
+      <c r="B39" s="144"/>
+      <c r="C39" s="144"/>
+      <c r="D39" s="197"/>
+      <c r="E39" s="145"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="205">
+      <c r="C40" s="51"/>
+      <c r="D40" s="207">
         <v>628219.53</v>
       </c>
-      <c r="E40" s="161" t="s">
+      <c r="E40" s="160" t="s">
         <v>117</v>
       </c>
-      <c r="G40" s="123"/>
+      <c r="G40" s="122"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="205">
+      <c r="C41" s="51"/>
+      <c r="D41" s="207">
         <v>10602.27</v>
       </c>
-      <c r="E41" s="161" t="s">
+      <c r="E41" s="160" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2302,19 +2295,19 @@
         <v>77</v>
       </c>
       <c r="B42" s="5"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="205">
+      <c r="C42" s="51"/>
+      <c r="D42" s="207">
         <v>75532.289999999994</v>
       </c>
-      <c r="E42" s="152" t="str">
+      <c r="E42" s="151" t="str">
         <f>E41</f>
         <v>Debito 18/08</v>
       </c>
-      <c r="F42" s="43">
+      <c r="F42" s="42">
         <f>D42+D41</f>
         <v>86134.56</v>
       </c>
-      <c r="G42" s="137"/>
+      <c r="G42" s="136"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
@@ -2322,10 +2315,10 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="203">
+      <c r="D43" s="154">
         <v>5733.45</v>
       </c>
-      <c r="E43" s="161" t="s">
+      <c r="E43" s="160" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2336,10 +2329,10 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="203">
+      <c r="D44" s="154">
         <v>99230.87</v>
       </c>
-      <c r="E44" s="153" t="str">
+      <c r="E44" s="152" t="str">
         <f>E43</f>
         <v>Debito 12/08</v>
       </c>
@@ -2351,56 +2344,56 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="203">
+      <c r="D45" s="154">
         <v>51601.05</v>
       </c>
-      <c r="E45" s="154" t="str">
+      <c r="E45" s="153" t="str">
         <f>E44</f>
         <v>Debito 12/08</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="145"/>
-      <c r="C46" s="145"/>
-      <c r="D46" s="199"/>
-      <c r="E46" s="144">
+      <c r="B46" s="144"/>
+      <c r="C46" s="144"/>
+      <c r="D46" s="198"/>
+      <c r="E46" s="143">
         <f>SUM(D40:D45)</f>
         <v>870919.46000000008</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="145"/>
-      <c r="C47" s="145"/>
-      <c r="D47" s="198"/>
-      <c r="E47" s="146"/>
+      <c r="B47" s="144"/>
+      <c r="C47" s="144"/>
+      <c r="D47" s="197"/>
+      <c r="E47" s="145"/>
     </row>
     <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="155"/>
+      <c r="B48" s="154"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="203">
+      <c r="D48" s="154">
         <v>46283.07</v>
       </c>
-      <c r="E48" s="156"/>
+      <c r="E48" s="155"/>
     </row>
     <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="155"/>
+      <c r="B49" s="154"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="155">
-        <v>0</v>
-      </c>
-      <c r="E49" s="156"/>
+      <c r="D49" s="154">
+        <v>0</v>
+      </c>
+      <c r="E49" s="155"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
@@ -2408,157 +2401,157 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="203">
+      <c r="D50" s="154">
         <v>41246.76</v>
       </c>
-      <c r="E50" s="156" t="s">
+      <c r="E50" s="155" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="208" t="s">
+      <c r="A51" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="209"/>
+      <c r="B51" s="212"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="203">
+      <c r="D51" s="154">
         <v>530549.97</v>
       </c>
-      <c r="E51" s="154" t="s">
+      <c r="E51" s="153" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="200"/>
-      <c r="E52" s="144">
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="199"/>
+      <c r="E52" s="143">
         <f>SUM(D48:D51)</f>
         <v>618079.79999999993</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="35" t="s">
+      <c r="A53" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="196"/>
-      <c r="E53" s="147"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="195"/>
+      <c r="E53" s="146"/>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="157" t="s">
+      <c r="A54" s="156" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="151"/>
+      <c r="B54" s="150"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="203">
+      <c r="D54" s="154">
         <v>102500</v>
       </c>
-      <c r="E54" s="156" t="s">
+      <c r="E54" s="155" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="157" t="s">
+      <c r="A55" s="156" t="s">
         <v>93</v>
       </c>
-      <c r="B55" s="151"/>
+      <c r="B55" s="150"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="155">
-        <v>0</v>
-      </c>
-      <c r="E55" s="156"/>
+      <c r="D55" s="154">
+        <v>0</v>
+      </c>
+      <c r="E55" s="155"/>
     </row>
     <row r="56" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="243" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" s="202"/>
+      <c r="A56" s="208" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="201"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="127">
+      <c r="D56" s="105">
         <f>750000/3</f>
         <v>250000</v>
       </c>
-      <c r="E56" s="244" t="s">
+      <c r="E56" s="203" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="208" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="201"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="105">
+        <v>60000</v>
+      </c>
+      <c r="E57" s="203" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="243" t="s">
-        <v>127</v>
-      </c>
-      <c r="B57" s="202"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="127">
-        <v>60000</v>
-      </c>
-      <c r="E57" s="244" t="s">
-        <v>128</v>
-      </c>
-    </row>
     <row r="58" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="157" t="s">
+      <c r="A58" s="156" t="s">
         <v>124</v>
       </c>
-      <c r="B58" s="202"/>
+      <c r="B58" s="201"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="127">
+      <c r="D58" s="105">
         <v>78600</v>
       </c>
-      <c r="E58" s="156" t="s">
+      <c r="E58" s="155" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="208" t="s">
+      <c r="A59" s="211" t="s">
         <v>115</v>
       </c>
-      <c r="B59" s="209"/>
+      <c r="B59" s="212"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="127">
+      <c r="D59" s="105">
         <v>333100</v>
       </c>
-      <c r="E59" s="156" t="s">
+      <c r="E59" s="155" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="208" t="s">
+      <c r="A60" s="211" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="209"/>
+      <c r="B60" s="212"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="127">
+      <c r="D60" s="105">
         <v>95700</v>
       </c>
-      <c r="E60" s="156" t="s">
+      <c r="E60" s="155" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="148">
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="147">
         <f>SUM(D54:D60)</f>
         <v>919900</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="67"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="194"/>
-      <c r="E62" s="147"/>
+      <c r="B62" s="66"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="193"/>
+      <c r="E62" s="146"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
@@ -2566,10 +2559,10 @@
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="155">
+      <c r="D63" s="154">
         <v>67713</v>
       </c>
-      <c r="E63" s="149"/>
+      <c r="E63" s="148"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
@@ -2577,126 +2570,127 @@
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="203">
-        <v>67627.39</v>
-      </c>
-      <c r="E64" s="40"/>
+      <c r="D64" s="154">
+        <f>800+168+5112.79+67627.39</f>
+        <v>73708.179999999993</v>
+      </c>
+      <c r="E64" s="39"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="51" t="s">
+      <c r="A65" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B65" s="51"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="201"/>
-      <c r="E65" s="103">
+      <c r="B65" s="50"/>
+      <c r="C65" s="50"/>
+      <c r="D65" s="200"/>
+      <c r="E65" s="102">
         <f>SUM(D63:D64)</f>
-        <v>135340.39000000001</v>
+        <v>141421.18</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
-      <c r="D66" s="102"/>
-      <c r="E66" s="109"/>
+      <c r="D66" s="101"/>
+      <c r="E66" s="108"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="110"/>
-      <c r="E67" s="111">
-        <f>4880009.37-4132288.74</f>
-        <v>747720.62999999989</v>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="109"/>
+      <c r="E67" s="110">
+        <f>4880009.37+700000-3739046.44</f>
+        <v>1840962.9300000002</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
-      <c r="D68" s="112"/>
-      <c r="E68" s="113"/>
-      <c r="F68" s="43"/>
+      <c r="D68" s="111"/>
+      <c r="E68" s="112"/>
+      <c r="F68" s="42"/>
     </row>
     <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B69" s="10"/>
+      <c r="B69" s="9"/>
       <c r="C69" s="4"/>
-      <c r="D69" s="114"/>
-      <c r="E69" s="115">
+      <c r="D69" s="113"/>
+      <c r="E69" s="114">
         <f>(SUM(E27:E67))</f>
-        <v>4480686.2799999993</v>
-      </c>
-      <c r="F69" s="137">
-        <v>0</v>
-      </c>
-      <c r="G69" s="43"/>
-      <c r="H69" s="123"/>
-      <c r="I69" s="123"/>
-      <c r="J69" s="123"/>
-      <c r="K69" s="123"/>
-      <c r="L69" s="123"/>
+        <v>5580009.3700000001</v>
+      </c>
+      <c r="F69" s="136">
+        <v>0</v>
+      </c>
+      <c r="G69" s="42"/>
+      <c r="H69" s="122"/>
+      <c r="I69" s="122"/>
+      <c r="J69" s="122"/>
+      <c r="K69" s="122"/>
+      <c r="L69" s="122"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D70" s="112"/>
-      <c r="E70" s="112"/>
-      <c r="H70" s="123"/>
-      <c r="I70" s="123"/>
-      <c r="J70" s="123"/>
-      <c r="K70" s="123"/>
-      <c r="L70" s="123"/>
+      <c r="D70" s="111"/>
+      <c r="E70" s="111"/>
+      <c r="H70" s="122"/>
+      <c r="I70" s="122"/>
+      <c r="J70" s="122"/>
+      <c r="K70" s="122"/>
+      <c r="L70" s="122"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="112"/>
-      <c r="E71" s="112"/>
-      <c r="H71" s="160"/>
+      <c r="D71" s="111"/>
+      <c r="E71" s="111"/>
+      <c r="H71" s="159"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="116"/>
-      <c r="E72" s="117"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="115"/>
+      <c r="E72" s="116"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="208"/>
-      <c r="B73" s="209"/>
+      <c r="A73" s="211"/>
+      <c r="B73" s="212"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="127"/>
-      <c r="E73" s="104"/>
+      <c r="D73" s="126"/>
+      <c r="E73" s="103"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="208"/>
-      <c r="B74" s="209"/>
+      <c r="A74" s="211"/>
+      <c r="B74" s="212"/>
       <c r="C74" s="5"/>
-      <c r="D74" s="106"/>
-      <c r="E74" s="104"/>
+      <c r="D74" s="105"/>
+      <c r="E74" s="103"/>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="210"/>
-      <c r="B75" s="211"/>
+      <c r="A75" s="213"/>
+      <c r="B75" s="214"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="106"/>
-      <c r="E75" s="104"/>
+      <c r="D75" s="105"/>
+      <c r="E75" s="103"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="105"/>
-      <c r="B76" s="107"/>
+      <c r="A76" s="104"/>
+      <c r="B76" s="106"/>
       <c r="C76" s="5"/>
-      <c r="D76" s="106"/>
-      <c r="E76" s="104"/>
+      <c r="D76" s="105"/>
+      <c r="E76" s="103"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="49"/>
-      <c r="B77" s="48"/>
-      <c r="C77" s="48"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="58">
+      <c r="A77" s="48"/>
+      <c r="B77" s="47"/>
+      <c r="C77" s="47"/>
+      <c r="D77" s="57"/>
+      <c r="E77" s="57">
         <f>SUM(D73:D76)</f>
         <v>0</v>
       </c>
@@ -2704,298 +2698,298 @@
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="30" t="s">
+      <c r="A80" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B80" s="30"/>
-      <c r="C80" s="30"/>
-      <c r="D80" s="31"/>
-      <c r="E80" s="101"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="100"/>
     </row>
     <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="10"/>
+      <c r="B82" s="9"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="68">
+      <c r="E82" s="67">
         <f>E77+E80</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="99" t="s">
+      <c r="A84" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="B84" s="100">
+      <c r="B84" s="99">
         <f>E69</f>
-        <v>4480686.2799999993</v>
+        <v>5580009.3700000001</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="99" t="s">
+      <c r="A85" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B85" s="100">
+      <c r="B85" s="99">
         <f>E69-E67</f>
-        <v>3732965.6499999994</v>
+        <v>3739046.44</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="99" t="s">
+      <c r="A86" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B86" s="100">
+      <c r="B86" s="99">
         <f>E82-E80</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="99" t="s">
+      <c r="A87" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="B87" s="100">
+      <c r="B87" s="99">
         <f>E82</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D89" s="123"/>
-      <c r="E89" s="123"/>
+      <c r="D89" s="122"/>
+      <c r="E89" s="122"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D90" s="123"/>
-      <c r="E90" s="123"/>
+      <c r="D90" s="122"/>
+      <c r="E90" s="122"/>
     </row>
     <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="23" t="s">
+      <c r="A91" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B91" s="124"/>
-      <c r="C91" s="24"/>
+      <c r="B91" s="123"/>
+      <c r="C91" s="23"/>
     </row>
     <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="33"/>
-      <c r="B92" s="59">
-        <v>0</v>
-      </c>
-      <c r="C92" s="26"/>
+      <c r="A92" s="32"/>
+      <c r="B92" s="58">
+        <v>0</v>
+      </c>
+      <c r="C92" s="25"/>
     </row>
     <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="25" t="s">
+      <c r="A93" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B93" s="40">
+      <c r="B93" s="39">
         <f>PRORRATEO!F29</f>
         <v>4938034.42</v>
       </c>
-      <c r="C93" s="24"/>
+      <c r="C93" s="23"/>
     </row>
     <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="25"/>
-      <c r="B94" s="40">
-        <v>0</v>
-      </c>
-      <c r="C94" s="24"/>
+      <c r="A94" s="24"/>
+      <c r="B94" s="39">
+        <v>0</v>
+      </c>
+      <c r="C94" s="23"/>
     </row>
     <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="25" t="s">
+      <c r="A95" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B95" s="108">
+      <c r="B95" s="107">
         <f>B116</f>
         <v>0</v>
       </c>
-      <c r="C95" s="24"/>
+      <c r="C95" s="23"/>
     </row>
     <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="28"/>
-      <c r="B96" s="47"/>
-      <c r="C96" s="24"/>
+      <c r="A96" s="27"/>
+      <c r="B96" s="46"/>
+      <c r="C96" s="23"/>
     </row>
     <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="122" t="s">
+      <c r="A97" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="B97" s="47"/>
-      <c r="C97" s="24"/>
+      <c r="B97" s="46"/>
+      <c r="C97" s="23"/>
     </row>
     <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="39" t="s">
+      <c r="A98" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B98" s="47">
+      <c r="B98" s="46">
         <f>-B85</f>
-        <v>-3732965.6499999994</v>
-      </c>
-      <c r="C98" s="24"/>
+        <v>-3739046.44</v>
+      </c>
+      <c r="C98" s="23"/>
     </row>
     <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="28" t="s">
+      <c r="A99" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B99" s="47">
+      <c r="B99" s="46">
         <f>-(B86)</f>
         <v>0</v>
       </c>
-      <c r="C99" s="24"/>
+      <c r="C99" s="23"/>
     </row>
     <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="32" t="s">
+      <c r="A100" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B100" s="59">
+      <c r="B100" s="58">
         <f>SUM(B92:B99)</f>
-        <v>1205068.7700000005</v>
-      </c>
-      <c r="C100" s="27"/>
-      <c r="D100" s="43"/>
+        <v>1198987.98</v>
+      </c>
+      <c r="C100" s="26"/>
+      <c r="D100" s="42"/>
     </row>
     <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="41"/>
-      <c r="C101" s="27"/>
-      <c r="D101" s="43"/>
-      <c r="E101" s="125"/>
-      <c r="F101" s="126"/>
+      <c r="B101" s="40"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="42"/>
+      <c r="E101" s="124"/>
+      <c r="F101" s="125"/>
     </row>
     <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="42"/>
-      <c r="C102" s="27"/>
-    </row>
-    <row r="103" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="41"/>
+      <c r="C102" s="26"/>
+    </row>
+    <row r="103" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
-      <c r="B103" s="41"/>
-      <c r="C103" s="37"/>
-    </row>
-    <row r="104" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="130" t="s">
+      <c r="B103" s="40"/>
+      <c r="C103" s="36"/>
+    </row>
+    <row r="104" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="B104" s="166">
-        <v>-2936183.8760999963</v>
-      </c>
-      <c r="C104" s="37"/>
-      <c r="D104" s="46"/>
+      <c r="B104" s="165">
+        <v>-2699002.0460999953</v>
+      </c>
+      <c r="C104" s="36"/>
+      <c r="D104" s="45"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="54" t="s">
+      <c r="A105" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="B105" s="135">
+      <c r="B105" s="134">
         <f>-B85</f>
-        <v>-3732965.6499999994</v>
+        <v>-3739046.44</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="54" t="s">
+      <c r="A106" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B106" s="135">
+      <c r="B106" s="134">
         <f>-B86</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="54" t="s">
+      <c r="A107" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="B107" s="135">
+      <c r="B107" s="134">
         <f>B116</f>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="54" t="s">
+      <c r="A108" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="B108" s="136">
+      <c r="B108" s="135">
         <f>PRORRATEO!F29</f>
         <v>4938034.42</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="133" t="s">
+      <c r="A109" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="B109" s="134">
+      <c r="B109" s="133">
         <f>SUM(B104:C108)</f>
-        <v>-1731115.1060999958</v>
+        <v>-1500014.0660999957</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="131"/>
-      <c r="B110" s="131"/>
+      <c r="A110" s="130"/>
+      <c r="B110" s="130"/>
     </row>
     <row r="111" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="207" t="s">
+      <c r="A112" s="210" t="s">
         <v>32</v>
       </c>
-      <c r="B112" s="207"/>
-      <c r="C112" s="207"/>
+      <c r="B112" s="210"/>
+      <c r="C112" s="210"/>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="207"/>
-      <c r="B113" s="207"/>
-      <c r="C113" s="207"/>
+      <c r="A113" s="210"/>
+      <c r="B113" s="210"/>
+      <c r="C113" s="210"/>
     </row>
     <row r="114" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="119"/>
-      <c r="B114" s="36"/>
-      <c r="C114" s="36">
+      <c r="A114" s="118"/>
+      <c r="B114" s="35"/>
+      <c r="C114" s="35">
         <v>40000</v>
       </c>
-      <c r="E114" s="137"/>
+      <c r="E114" s="136"/>
     </row>
     <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="119"/>
-      <c r="B115" s="121"/>
-      <c r="C115" s="118"/>
-      <c r="D115" s="137"/>
+      <c r="A115" s="118"/>
+      <c r="B115" s="120"/>
+      <c r="C115" s="117"/>
+      <c r="D115" s="136"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="44" t="s">
+      <c r="A116" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B116" s="120">
+      <c r="B116" s="119">
         <f>SUM(B114:B115)</f>
         <v>0</v>
       </c>
-      <c r="C116" s="45"/>
+      <c r="C116" s="44"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M117" s="8"/>
     </row>
     <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="206"/>
-      <c r="B118" s="206"/>
-      <c r="C118" s="206"/>
-      <c r="D118" s="206"/>
-      <c r="E118" s="206"/>
+      <c r="A118" s="209"/>
+      <c r="B118" s="209"/>
+      <c r="C118" s="209"/>
+      <c r="D118" s="209"/>
+      <c r="E118" s="209"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="206"/>
-      <c r="B119" s="206"/>
-      <c r="C119" s="206"/>
-      <c r="D119" s="206"/>
-      <c r="E119" s="206"/>
+      <c r="A119" s="209"/>
+      <c r="B119" s="209"/>
+      <c r="C119" s="209"/>
+      <c r="D119" s="209"/>
+      <c r="E119" s="209"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="206"/>
-      <c r="B120" s="206"/>
-      <c r="C120" s="206"/>
-      <c r="D120" s="206"/>
-      <c r="E120" s="206"/>
+      <c r="A120" s="209"/>
+      <c r="B120" s="209"/>
+      <c r="C120" s="209"/>
+      <c r="D120" s="209"/>
+      <c r="E120" s="209"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="206"/>
-      <c r="B121" s="206"/>
-      <c r="C121" s="206"/>
-      <c r="D121" s="206"/>
-      <c r="E121" s="206"/>
+      <c r="A121" s="209"/>
+      <c r="B121" s="209"/>
+      <c r="C121" s="209"/>
+      <c r="D121" s="209"/>
+      <c r="E121" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3049,16 +3043,16 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
@@ -3070,7 +3064,7 @@
         <v>82</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="158">
+      <c r="F2" s="157">
         <v>86134.56</v>
       </c>
       <c r="G2" s="6"/>
@@ -3081,13 +3075,12 @@
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
-      <c r="M2" s="129">
-        <f>R4-F2</f>
-        <v>4880009.370000001</v>
-      </c>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="22"/>
+      <c r="M2" s="128">
+        <v>5580009.3700000001</v>
+      </c>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="21"/>
     </row>
     <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
@@ -3102,525 +3095,525 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="60"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="59"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="216" t="s">
+      <c r="A4" s="219" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="219" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="219" t="s">
+      <c r="E4" s="222" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="216" t="s">
+      <c r="F4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="226" t="s">
+      <c r="G4" s="229" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="219" t="s">
+      <c r="H4" s="222" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="219" t="s">
+      <c r="I4" s="222" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="219" t="s">
+      <c r="J4" s="222" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="219" t="s">
+      <c r="K4" s="222" t="s">
         <v>109</v>
       </c>
-      <c r="L4" s="229" t="s">
+      <c r="L4" s="232" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="63" t="s">
+      <c r="M4" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="224" t="s">
+      <c r="N4" s="227" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="221" t="s">
+      <c r="O4" s="224" t="s">
         <v>36</v>
       </c>
-      <c r="R4" s="129">
+      <c r="R4" s="128">
         <v>4966143.9300000006</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="218"/>
-      <c r="B5" s="218"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="218"/>
-      <c r="E5" s="220"/>
-      <c r="F5" s="218"/>
-      <c r="G5" s="227"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="228"/>
-      <c r="J5" s="220"/>
-      <c r="K5" s="220"/>
-      <c r="L5" s="230"/>
-      <c r="M5" s="61" t="str">
+      <c r="A5" s="221"/>
+      <c r="B5" s="221"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="221"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="221"/>
+      <c r="G5" s="230"/>
+      <c r="H5" s="223"/>
+      <c r="I5" s="231"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="233"/>
+      <c r="M5" s="60" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="N5" s="225"/>
-      <c r="O5" s="222"/>
+      <c r="N5" s="228"/>
+      <c r="O5" s="225"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="162">
+      <c r="A6" s="161">
         <v>1</v>
       </c>
-      <c r="B6" s="162" t="s">
+      <c r="B6" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="73">
+      <c r="C6" s="63"/>
+      <c r="D6" s="72">
         <v>6.69</v>
       </c>
-      <c r="E6" s="74">
+      <c r="E6" s="73">
         <v>332235.01</v>
       </c>
-      <c r="F6" s="241">
+      <c r="F6" s="74">
         <f>E6</f>
         <v>332235.01</v>
       </c>
-      <c r="G6" s="76">
+      <c r="G6" s="75">
         <f t="shared" ref="G6:G23" si="0">E6-F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="76">
+      <c r="H6" s="75">
         <f>IF(G6&gt;0,G6*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="77">
-        <v>0</v>
-      </c>
-      <c r="J6" s="78">
+      <c r="I6" s="76">
+        <v>0</v>
+      </c>
+      <c r="J6" s="77">
         <f>M$2*D6/100</f>
-        <v>326472.62685300008</v>
-      </c>
-      <c r="K6" s="159"/>
-      <c r="L6" s="159">
+        <v>373302.62685300002</v>
+      </c>
+      <c r="K6" s="158"/>
+      <c r="L6" s="158">
         <f t="shared" ref="L6:L23" si="1">F$2*D6/100</f>
         <v>5762.4020639999999</v>
       </c>
-      <c r="M6" s="80">
+      <c r="M6" s="79">
         <f>ROUND(SUM(G6:L6),0) + P6</f>
-        <v>332235.01</v>
-      </c>
-      <c r="N6" s="81">
+        <v>379065.01</v>
+      </c>
+      <c r="N6" s="80">
         <f>ROUND(M6*6% + M6,0) + P6</f>
-        <v>352169.01</v>
-      </c>
-      <c r="O6" s="82">
+        <v>401809.01</v>
+      </c>
+      <c r="O6" s="81">
         <f>ROUND(M6*3%,0) + M6</f>
-        <v>342202.01</v>
-      </c>
-      <c r="P6" s="43">
+        <v>390437.01</v>
+      </c>
+      <c r="P6" s="42">
         <v>0.01</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="162">
+      <c r="A7" s="161">
         <f>A6+1</f>
         <v>2</v>
       </c>
-      <c r="B7" s="162" t="s">
+      <c r="B7" s="161" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="73">
+      <c r="C7" s="64"/>
+      <c r="D7" s="72">
         <v>5.88</v>
       </c>
-      <c r="E7" s="74">
+      <c r="E7" s="73">
         <v>2898882.02</v>
       </c>
-      <c r="F7" s="75"/>
-      <c r="G7" s="76">
+      <c r="F7" s="74"/>
+      <c r="G7" s="75">
         <f t="shared" si="0"/>
         <v>2898882.02</v>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="75">
         <f t="shared" ref="H7:H23" si="2">IF(G7&gt;0,G7*3%,0)</f>
         <v>86966.460599999991</v>
       </c>
-      <c r="I7" s="77">
-        <v>0</v>
-      </c>
-      <c r="J7" s="78">
+      <c r="I7" s="76">
+        <v>0</v>
+      </c>
+      <c r="J7" s="77">
         <f t="shared" ref="J7:J23" si="3">M$2*D7%</f>
-        <v>286944.55095600005</v>
-      </c>
-      <c r="K7" s="159">
+        <v>328104.55095599999</v>
+      </c>
+      <c r="K7" s="158">
         <f>24000+99500</f>
         <v>123500</v>
       </c>
-      <c r="L7" s="159">
+      <c r="L7" s="158">
         <f t="shared" si="1"/>
         <v>5064.7121280000001</v>
       </c>
-      <c r="M7" s="80">
+      <c r="M7" s="79">
         <f t="shared" ref="M7:M23" si="4">ROUND(SUM(G7:L7),0) + P7</f>
-        <v>3401358.02</v>
-      </c>
-      <c r="N7" s="81">
+        <v>3442518.02</v>
+      </c>
+      <c r="N7" s="80">
         <f t="shared" ref="N7:N23" si="5">ROUND(M7*6% + M7,0) + P7</f>
-        <v>3605440.02</v>
-      </c>
-      <c r="O7" s="82">
+        <v>3649069.02</v>
+      </c>
+      <c r="O7" s="81">
         <f t="shared" ref="O7:O23" si="6">ROUND(M7*3%,0) + M7</f>
-        <v>3503399.02</v>
-      </c>
-      <c r="P7" s="43">
+        <v>3545794.02</v>
+      </c>
+      <c r="P7" s="42">
         <f>P6+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="Q7" s="43"/>
+      <c r="Q7" s="42"/>
     </row>
     <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162">
+      <c r="A8" s="161">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
       </c>
-      <c r="B8" s="162" t="s">
+      <c r="B8" s="161" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="163"/>
-      <c r="D8" s="164">
+      <c r="C8" s="162"/>
+      <c r="D8" s="163">
         <v>6.65</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="74">
         <v>560853.03</v>
       </c>
-      <c r="F8" s="75">
-        <v>0</v>
-      </c>
-      <c r="G8" s="76">
+      <c r="F8" s="74">
+        <v>0</v>
+      </c>
+      <c r="G8" s="75">
         <f t="shared" si="0"/>
         <v>560853.03</v>
       </c>
-      <c r="H8" s="76">
+      <c r="H8" s="75">
         <f t="shared" si="2"/>
         <v>16825.590899999999</v>
       </c>
-      <c r="I8" s="77">
-        <v>0</v>
-      </c>
-      <c r="J8" s="78">
+      <c r="I8" s="76">
+        <v>0</v>
+      </c>
+      <c r="J8" s="77">
         <f t="shared" si="3"/>
-        <v>324520.62310500006</v>
-      </c>
-      <c r="K8" s="159"/>
-      <c r="L8" s="159">
+        <v>371070.62310500001</v>
+      </c>
+      <c r="K8" s="158"/>
+      <c r="L8" s="158">
         <f t="shared" si="1"/>
         <v>5727.9482400000006</v>
       </c>
-      <c r="M8" s="80">
+      <c r="M8" s="79">
         <f t="shared" si="4"/>
-        <v>907927.03</v>
-      </c>
-      <c r="N8" s="81">
+        <v>954477.03</v>
+      </c>
+      <c r="N8" s="80">
         <f t="shared" si="5"/>
-        <v>962403.03</v>
-      </c>
-      <c r="O8" s="82">
+        <v>1011746.03</v>
+      </c>
+      <c r="O8" s="81">
         <f t="shared" si="6"/>
-        <v>935165.03</v>
-      </c>
-      <c r="P8" s="43">
+        <v>983111.03</v>
+      </c>
+      <c r="P8" s="42">
         <f t="shared" ref="P8:P24" si="8">P7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162">
+      <c r="A9" s="161">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="161" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="73">
+      <c r="C9" s="64"/>
+      <c r="D9" s="72">
         <v>6.73</v>
       </c>
-      <c r="E9" s="74">
+      <c r="E9" s="73">
         <v>334221.03999999998</v>
       </c>
-      <c r="F9" s="241">
+      <c r="F9" s="74">
         <f>E9</f>
         <v>334221.03999999998</v>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="77">
-        <v>0</v>
-      </c>
-      <c r="J9" s="78">
+      <c r="I9" s="76">
+        <v>0</v>
+      </c>
+      <c r="J9" s="77">
         <f t="shared" si="3"/>
-        <v>328424.63060100004</v>
-      </c>
-      <c r="K9" s="159"/>
-      <c r="L9" s="159">
+        <v>375534.63060099998</v>
+      </c>
+      <c r="K9" s="158"/>
+      <c r="L9" s="158">
         <f t="shared" si="1"/>
         <v>5796.855888</v>
       </c>
-      <c r="M9" s="80">
+      <c r="M9" s="79">
         <f t="shared" si="4"/>
-        <v>334221.03999999998</v>
-      </c>
-      <c r="N9" s="81">
+        <v>381331.04</v>
+      </c>
+      <c r="N9" s="80">
         <f t="shared" si="5"/>
-        <v>354274.04</v>
-      </c>
-      <c r="O9" s="82">
+        <v>404211.04</v>
+      </c>
+      <c r="O9" s="81">
         <f t="shared" si="6"/>
-        <v>344248.04</v>
-      </c>
-      <c r="P9" s="43">
+        <v>392771.04</v>
+      </c>
+      <c r="P9" s="42">
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
-      <c r="R9" s="43"/>
+      <c r="R9" s="42"/>
     </row>
     <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="162">
+      <c r="A10" s="161">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="B10" s="162" t="s">
+      <c r="B10" s="161" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="73">
+      <c r="C10" s="64"/>
+      <c r="D10" s="72">
         <v>8.0399999999999991</v>
       </c>
-      <c r="E10" s="74">
+      <c r="E10" s="73">
         <v>834850.05</v>
       </c>
-      <c r="F10" s="241">
+      <c r="F10" s="74">
         <v>834850.05</v>
       </c>
-      <c r="G10" s="76">
+      <c r="G10" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="76">
+      <c r="H10" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I10" s="77">
-        <v>0</v>
-      </c>
-      <c r="J10" s="78">
+      <c r="I10" s="76">
+        <v>0</v>
+      </c>
+      <c r="J10" s="77">
         <f t="shared" si="3"/>
-        <v>392352.753348</v>
-      </c>
-      <c r="K10" s="159"/>
-      <c r="L10" s="159">
+        <v>448632.75334799994</v>
+      </c>
+      <c r="K10" s="158"/>
+      <c r="L10" s="158">
         <f t="shared" si="1"/>
         <v>6925.2186239999983</v>
       </c>
-      <c r="M10" s="80">
+      <c r="M10" s="79">
         <f t="shared" si="4"/>
-        <v>399278.05</v>
-      </c>
-      <c r="N10" s="81">
+        <v>455558.05</v>
+      </c>
+      <c r="N10" s="80">
         <f t="shared" si="5"/>
-        <v>423235.05</v>
-      </c>
-      <c r="O10" s="82">
+        <v>482892.05</v>
+      </c>
+      <c r="O10" s="81">
         <f t="shared" si="6"/>
-        <v>411256.05</v>
-      </c>
-      <c r="P10" s="43">
+        <v>469225.05</v>
+      </c>
+      <c r="P10" s="42">
         <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
       <c r="Q10" t="s">
         <v>97</v>
       </c>
-      <c r="R10" s="43"/>
+      <c r="R10" s="42"/>
     </row>
     <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="162">
+      <c r="A11" s="161">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="B11" s="162" t="s">
+      <c r="B11" s="161" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="73">
+      <c r="C11" s="63"/>
+      <c r="D11" s="72">
         <v>4.7300000000000004</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E11" s="73">
         <v>234899.06</v>
       </c>
-      <c r="F11" s="241">
+      <c r="F11" s="74">
         <f>E11+RESUMEN!D56</f>
         <v>484899.06</v>
       </c>
-      <c r="G11" s="76">
+      <c r="G11" s="75">
         <f t="shared" si="0"/>
         <v>-250000</v>
       </c>
-      <c r="H11" s="76">
+      <c r="H11" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="77">
-        <v>0</v>
-      </c>
-      <c r="J11" s="78">
+      <c r="I11" s="76">
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
         <f t="shared" si="3"/>
-        <v>230824.44320100005</v>
-      </c>
-      <c r="K11" s="159"/>
-      <c r="L11" s="159">
+        <v>263934.44320099999</v>
+      </c>
+      <c r="K11" s="158"/>
+      <c r="L11" s="158">
         <f t="shared" si="1"/>
         <v>4074.1646880000003</v>
       </c>
-      <c r="M11" s="80">
+      <c r="M11" s="79">
         <f t="shared" si="4"/>
-        <v>-15100.94</v>
-      </c>
-      <c r="N11" s="81">
+        <v>18009.060000000001</v>
+      </c>
+      <c r="N11" s="80">
         <f t="shared" si="5"/>
-        <v>-16006.94</v>
-      </c>
-      <c r="O11" s="82">
+        <v>19090.060000000001</v>
+      </c>
+      <c r="O11" s="81">
         <f t="shared" si="6"/>
-        <v>-15553.94</v>
-      </c>
-      <c r="P11" s="43">
+        <v>18549.060000000001</v>
+      </c>
+      <c r="P11" s="42">
         <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="179">
+      <c r="A12" s="178">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="B12" s="179" t="s">
+      <c r="B12" s="178" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="179"/>
-      <c r="D12" s="180">
+      <c r="C12" s="178"/>
+      <c r="D12" s="179">
         <v>5.67</v>
       </c>
-      <c r="E12" s="181">
+      <c r="E12" s="180">
         <v>1048899.07</v>
       </c>
-      <c r="F12" s="242">
+      <c r="F12" s="180">
         <v>250000</v>
       </c>
-      <c r="G12" s="183">
+      <c r="G12" s="182">
         <f t="shared" si="0"/>
         <v>798899.07000000007</v>
       </c>
-      <c r="H12" s="183">
+      <c r="H12" s="182">
         <f t="shared" si="2"/>
         <v>23966.972100000003</v>
       </c>
-      <c r="I12" s="182">
-        <v>0</v>
-      </c>
-      <c r="J12" s="184">
+      <c r="I12" s="181">
+        <v>0</v>
+      </c>
+      <c r="J12" s="183">
         <f t="shared" si="3"/>
-        <v>276696.53127900005</v>
-      </c>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185">
+        <v>316386.53127899999</v>
+      </c>
+      <c r="K12" s="184"/>
+      <c r="L12" s="184">
         <f t="shared" si="1"/>
         <v>4883.8295519999992</v>
       </c>
-      <c r="M12" s="186">
+      <c r="M12" s="185">
         <f t="shared" si="4"/>
-        <v>1104446.07</v>
-      </c>
-      <c r="N12" s="187">
+        <v>1144136.07</v>
+      </c>
+      <c r="N12" s="186">
         <f t="shared" si="5"/>
-        <v>1170713.07</v>
-      </c>
-      <c r="O12" s="188">
+        <v>1212784.07</v>
+      </c>
+      <c r="O12" s="187">
         <f t="shared" si="6"/>
-        <v>1137579.07</v>
-      </c>
-      <c r="P12" s="43">
+        <v>1178460.07</v>
+      </c>
+      <c r="P12" s="42">
         <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162">
+      <c r="A13" s="161">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="B13" s="162" t="s">
+      <c r="B13" s="161" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="73">
+      <c r="C13" s="64"/>
+      <c r="D13" s="72">
         <v>5.67</v>
       </c>
-      <c r="E13" s="74">
+      <c r="E13" s="73">
         <v>281580.08</v>
       </c>
-      <c r="F13" s="241">
-        <f>E13</f>
+      <c r="F13" s="74">
+        <f t="shared" ref="F13:F18" si="9">E13</f>
         <v>281580.08</v>
       </c>
-      <c r="G13" s="76">
+      <c r="G13" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="76">
+      <c r="H13" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="77">
-        <v>0</v>
-      </c>
-      <c r="J13" s="78">
+      <c r="I13" s="76">
+        <v>0</v>
+      </c>
+      <c r="J13" s="77">
         <f t="shared" si="3"/>
-        <v>276696.53127900005</v>
-      </c>
-      <c r="K13" s="159"/>
-      <c r="L13" s="159">
+        <v>316386.53127899999</v>
+      </c>
+      <c r="K13" s="158"/>
+      <c r="L13" s="158">
         <f t="shared" si="1"/>
         <v>4883.8295519999992</v>
       </c>
-      <c r="M13" s="80">
+      <c r="M13" s="79">
         <f t="shared" si="4"/>
-        <v>281580.08</v>
-      </c>
-      <c r="N13" s="81">
+        <v>321270.08</v>
+      </c>
+      <c r="N13" s="80">
         <f t="shared" si="5"/>
-        <v>298475.08</v>
-      </c>
-      <c r="O13" s="82">
+        <v>340546.08</v>
+      </c>
+      <c r="O13" s="81">
         <f t="shared" si="6"/>
-        <v>290027.08</v>
-      </c>
-      <c r="P13" s="43">
+        <v>330908.08</v>
+      </c>
+      <c r="P13" s="42">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
@@ -3629,337 +3622,337 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162">
+      <c r="A14" s="161">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="B14" s="162" t="s">
+      <c r="B14" s="161" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="73">
+      <c r="C14" s="64"/>
+      <c r="D14" s="72">
         <v>7.67</v>
       </c>
-      <c r="E14" s="74">
+      <c r="E14" s="73">
         <v>380903.09</v>
       </c>
-      <c r="F14" s="241">
-        <f>E14</f>
+      <c r="F14" s="74">
+        <f t="shared" si="9"/>
         <v>380903.09</v>
       </c>
-      <c r="G14" s="76">
+      <c r="G14" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="76">
+      <c r="H14" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="77">
-        <v>0</v>
-      </c>
-      <c r="J14" s="78">
+      <c r="I14" s="76">
+        <v>0</v>
+      </c>
+      <c r="J14" s="77">
         <f t="shared" si="3"/>
-        <v>374296.7186790001</v>
-      </c>
-      <c r="K14" s="159"/>
-      <c r="L14" s="159">
+        <v>427986.71867900004</v>
+      </c>
+      <c r="K14" s="158"/>
+      <c r="L14" s="158">
         <f t="shared" si="1"/>
         <v>6606.5207519999994</v>
       </c>
-      <c r="M14" s="80">
+      <c r="M14" s="79">
         <f t="shared" si="4"/>
-        <v>380903.09</v>
-      </c>
-      <c r="N14" s="81">
+        <v>434593.09</v>
+      </c>
+      <c r="N14" s="80">
         <f t="shared" si="5"/>
-        <v>403757.09</v>
-      </c>
-      <c r="O14" s="82">
+        <v>460669.09</v>
+      </c>
+      <c r="O14" s="81">
         <f t="shared" si="6"/>
-        <v>392330.09</v>
-      </c>
-      <c r="P14" s="43">
+        <v>447631.09</v>
+      </c>
+      <c r="P14" s="42">
         <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="162">
+      <c r="A15" s="161">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="B15" s="162" t="s">
+      <c r="B15" s="161" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="65"/>
-      <c r="D15" s="73">
+      <c r="C15" s="64"/>
+      <c r="D15" s="72">
         <v>4.9000000000000004</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="73">
         <v>243341.1</v>
       </c>
-      <c r="F15" s="241">
-        <f>E15</f>
+      <c r="F15" s="74">
+        <f t="shared" si="9"/>
         <v>243341.1</v>
       </c>
-      <c r="G15" s="76">
+      <c r="G15" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="76">
+      <c r="H15" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I15" s="77">
-        <v>0</v>
-      </c>
-      <c r="J15" s="78">
+      <c r="I15" s="76">
+        <v>0</v>
+      </c>
+      <c r="J15" s="77">
         <f t="shared" si="3"/>
-        <v>239120.45913000006</v>
-      </c>
-      <c r="K15" s="159"/>
-      <c r="L15" s="159">
+        <v>273420.45913000003</v>
+      </c>
+      <c r="K15" s="158"/>
+      <c r="L15" s="158">
         <f t="shared" si="1"/>
         <v>4220.5934400000006</v>
       </c>
-      <c r="M15" s="80">
+      <c r="M15" s="79">
         <f t="shared" si="4"/>
-        <v>243341.1</v>
-      </c>
-      <c r="N15" s="81">
+        <v>277641.09999999998</v>
+      </c>
+      <c r="N15" s="80">
         <f t="shared" si="5"/>
-        <v>257942.1</v>
-      </c>
-      <c r="O15" s="82">
+        <v>294300.09999999998</v>
+      </c>
+      <c r="O15" s="81">
         <f t="shared" si="6"/>
-        <v>250641.1</v>
-      </c>
-      <c r="P15" s="43">
+        <v>285970.09999999998</v>
+      </c>
+      <c r="P15" s="42">
         <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="162">
+      <c r="A16" s="161">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="B16" s="162" t="s">
+      <c r="B16" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="73">
+      <c r="C16" s="64"/>
+      <c r="D16" s="72">
         <v>5.63</v>
       </c>
-      <c r="E16" s="74">
+      <c r="E16" s="73">
         <v>288234.11</v>
       </c>
-      <c r="F16" s="241">
-        <f>E16</f>
+      <c r="F16" s="74">
+        <f t="shared" si="9"/>
         <v>288234.11</v>
       </c>
-      <c r="G16" s="76">
+      <c r="G16" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="76">
+      <c r="H16" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I16" s="77">
-        <v>0</v>
-      </c>
-      <c r="J16" s="78">
+      <c r="I16" s="76">
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
         <f t="shared" si="3"/>
-        <v>274744.52753100003</v>
-      </c>
-      <c r="K16" s="159"/>
-      <c r="L16" s="159">
+        <v>314154.52753099997</v>
+      </c>
+      <c r="K16" s="158"/>
+      <c r="L16" s="158">
         <f t="shared" si="1"/>
         <v>4849.375728</v>
       </c>
-      <c r="M16" s="80">
+      <c r="M16" s="79">
         <f t="shared" si="4"/>
-        <v>279594.11</v>
-      </c>
-      <c r="N16" s="81">
+        <v>319004.11</v>
+      </c>
+      <c r="N16" s="80">
         <f t="shared" si="5"/>
-        <v>296370.11</v>
-      </c>
-      <c r="O16" s="82">
+        <v>338144.11</v>
+      </c>
+      <c r="O16" s="81">
         <f t="shared" si="6"/>
-        <v>287982.11</v>
-      </c>
-      <c r="P16" s="43">
+        <v>328574.11</v>
+      </c>
+      <c r="P16" s="42">
         <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="162">
+      <c r="A17" s="161">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="B17" s="162" t="s">
+      <c r="B17" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="73">
+      <c r="C17" s="64"/>
+      <c r="D17" s="72">
         <v>5.55</v>
       </c>
-      <c r="E17" s="74">
+      <c r="E17" s="73">
         <v>275621.12</v>
       </c>
-      <c r="F17" s="241">
-        <f>E17</f>
+      <c r="F17" s="74">
+        <f t="shared" si="9"/>
         <v>275621.12</v>
       </c>
-      <c r="G17" s="76">
+      <c r="G17" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="76">
+      <c r="H17" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="77">
-        <v>0</v>
-      </c>
-      <c r="J17" s="78">
+      <c r="I17" s="76">
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
         <f t="shared" si="3"/>
-        <v>270840.52003500005</v>
-      </c>
-      <c r="K17" s="159"/>
-      <c r="L17" s="159">
+        <v>309690.52003499999</v>
+      </c>
+      <c r="K17" s="158"/>
+      <c r="L17" s="158">
         <f t="shared" si="1"/>
         <v>4780.4680799999996</v>
       </c>
-      <c r="M17" s="80">
+      <c r="M17" s="79">
         <f t="shared" si="4"/>
-        <v>275621.12</v>
-      </c>
-      <c r="N17" s="81">
+        <v>314471.12</v>
+      </c>
+      <c r="N17" s="80">
         <f t="shared" si="5"/>
-        <v>292158.12</v>
-      </c>
-      <c r="O17" s="82">
+        <v>333339.12</v>
+      </c>
+      <c r="O17" s="81">
         <f t="shared" si="6"/>
-        <v>283890.12</v>
-      </c>
-      <c r="P17" s="43">
+        <v>323905.12</v>
+      </c>
+      <c r="P17" s="42">
         <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="162">
+      <c r="A18" s="161">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="B18" s="162" t="s">
+      <c r="B18" s="161" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="73">
+      <c r="C18" s="64"/>
+      <c r="D18" s="72">
         <v>11.06</v>
       </c>
-      <c r="E18" s="74">
+      <c r="E18" s="73">
         <v>549256.13</v>
       </c>
-      <c r="F18" s="241">
-        <f>E18</f>
+      <c r="F18" s="74">
+        <f t="shared" si="9"/>
         <v>549256.13</v>
       </c>
-      <c r="G18" s="76">
+      <c r="G18" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="76">
+      <c r="H18" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I18" s="77">
-        <v>0</v>
-      </c>
-      <c r="J18" s="78">
+      <c r="I18" s="76">
+        <v>0</v>
+      </c>
+      <c r="J18" s="77">
         <f t="shared" si="3"/>
-        <v>539729.03632200009</v>
-      </c>
-      <c r="K18" s="159"/>
-      <c r="L18" s="159">
+        <v>617149.03632200009</v>
+      </c>
+      <c r="K18" s="158"/>
+      <c r="L18" s="158">
         <f t="shared" si="1"/>
         <v>9526.4823360000009</v>
       </c>
-      <c r="M18" s="80">
+      <c r="M18" s="79">
         <f t="shared" si="4"/>
-        <v>549256.13</v>
-      </c>
-      <c r="N18" s="81">
+        <v>626676.13</v>
+      </c>
+      <c r="N18" s="80">
         <f t="shared" si="5"/>
-        <v>582211.13</v>
-      </c>
-      <c r="O18" s="82">
+        <v>664277.13</v>
+      </c>
+      <c r="O18" s="81">
         <f t="shared" si="6"/>
-        <v>565734.13</v>
-      </c>
-      <c r="P18" s="43">
+        <v>645476.13</v>
+      </c>
+      <c r="P18" s="42">
         <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="162">
+      <c r="A19" s="161">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="B19" s="162" t="s">
+      <c r="B19" s="161" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="73">
+      <c r="C19" s="64"/>
+      <c r="D19" s="72">
         <v>3.3</v>
       </c>
-      <c r="E19" s="74">
+      <c r="E19" s="73">
         <v>166811.14000000001</v>
       </c>
-      <c r="F19" s="241">
+      <c r="F19" s="74">
         <f>1+161040.14</f>
         <v>161041.14000000001</v>
       </c>
-      <c r="G19" s="76">
+      <c r="G19" s="75">
         <f t="shared" si="0"/>
         <v>5770</v>
       </c>
-      <c r="H19" s="76">
+      <c r="H19" s="75">
         <f t="shared" si="2"/>
         <v>173.1</v>
       </c>
-      <c r="I19" s="77">
-        <v>0</v>
-      </c>
-      <c r="J19" s="78">
+      <c r="I19" s="76">
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
         <f t="shared" si="3"/>
-        <v>161040.30921000004</v>
-      </c>
-      <c r="K19" s="159"/>
-      <c r="L19" s="159">
+        <v>184140.30921000001</v>
+      </c>
+      <c r="K19" s="158"/>
+      <c r="L19" s="158">
         <f t="shared" si="1"/>
         <v>2842.4404799999993</v>
       </c>
-      <c r="M19" s="80">
+      <c r="M19" s="79">
         <f t="shared" si="4"/>
-        <v>169826.14</v>
-      </c>
-      <c r="N19" s="81">
+        <v>192926.14</v>
+      </c>
+      <c r="N19" s="80">
         <f t="shared" si="5"/>
-        <v>180016.14</v>
-      </c>
-      <c r="O19" s="82">
+        <v>204502.14</v>
+      </c>
+      <c r="O19" s="81">
         <f t="shared" si="6"/>
-        <v>174921.14</v>
-      </c>
-      <c r="P19" s="43">
+        <v>198714.14</v>
+      </c>
+      <c r="P19" s="42">
         <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
@@ -3968,57 +3961,57 @@
       </c>
     </row>
     <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="162">
+      <c r="A20" s="161">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="B20" s="162" t="s">
+      <c r="B20" s="161" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="163"/>
-      <c r="D20" s="164">
+      <c r="C20" s="162"/>
+      <c r="D20" s="163">
         <v>1.8</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="74">
         <v>89391.15</v>
       </c>
-      <c r="F20" s="241">
+      <c r="F20" s="74">
         <f>E20</f>
         <v>89391.15</v>
       </c>
-      <c r="G20" s="76">
+      <c r="G20" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="76">
+      <c r="H20" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="77">
-        <v>0</v>
-      </c>
-      <c r="J20" s="78">
+      <c r="I20" s="76">
+        <v>0</v>
+      </c>
+      <c r="J20" s="77">
         <f t="shared" si="3"/>
-        <v>87840.168660000025</v>
-      </c>
-      <c r="K20" s="159"/>
-      <c r="L20" s="159">
+        <v>100440.16866000001</v>
+      </c>
+      <c r="K20" s="158"/>
+      <c r="L20" s="158">
         <f t="shared" si="1"/>
         <v>1550.4220800000001</v>
       </c>
-      <c r="M20" s="80">
+      <c r="M20" s="79">
         <f t="shared" si="4"/>
-        <v>89391.15</v>
-      </c>
-      <c r="N20" s="81">
+        <v>101991.15</v>
+      </c>
+      <c r="N20" s="80">
         <f t="shared" si="5"/>
-        <v>94755.15</v>
-      </c>
-      <c r="O20" s="82">
+        <v>108111.15</v>
+      </c>
+      <c r="O20" s="81">
         <f t="shared" si="6"/>
-        <v>92073.15</v>
-      </c>
-      <c r="P20" s="43">
+        <v>105051.15</v>
+      </c>
+      <c r="P20" s="42">
         <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
@@ -4027,423 +4020,423 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="64">
+      <c r="A21" s="63">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
-      <c r="B21" s="64" t="s">
+      <c r="B21" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="73">
+      <c r="C21" s="63"/>
+      <c r="D21" s="72">
         <v>3.22</v>
       </c>
-      <c r="E21" s="74">
+      <c r="E21" s="73">
         <v>159910.16</v>
       </c>
-      <c r="F21" s="241">
-        <f t="shared" ref="F9:F23" si="9">E21</f>
+      <c r="F21" s="74">
+        <f t="shared" ref="F21" si="10">E21</f>
         <v>159910.16</v>
       </c>
-      <c r="G21" s="76">
+      <c r="G21" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="76">
+      <c r="H21" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I21" s="77">
-        <v>0</v>
-      </c>
-      <c r="J21" s="78">
+      <c r="I21" s="76">
+        <v>0</v>
+      </c>
+      <c r="J21" s="77">
         <f t="shared" si="3"/>
-        <v>157136.30171400003</v>
-      </c>
-      <c r="K21" s="159"/>
-      <c r="L21" s="159">
+        <v>179676.301714</v>
+      </c>
+      <c r="K21" s="158"/>
+      <c r="L21" s="158">
         <f t="shared" si="1"/>
         <v>2773.5328319999999</v>
       </c>
-      <c r="M21" s="80">
+      <c r="M21" s="79">
         <f t="shared" si="4"/>
-        <v>159910.16</v>
-      </c>
-      <c r="N21" s="81">
+        <v>182450.16</v>
+      </c>
+      <c r="N21" s="80">
         <f t="shared" si="5"/>
-        <v>169505.16</v>
-      </c>
-      <c r="O21" s="82">
+        <v>193397.16</v>
+      </c>
+      <c r="O21" s="81">
         <f t="shared" si="6"/>
-        <v>164707.16</v>
-      </c>
-      <c r="P21" s="43">
+        <v>187924.16</v>
+      </c>
+      <c r="P21" s="42">
         <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
-      <c r="Q21" s="123"/>
-      <c r="R21" s="165"/>
-      <c r="S21" s="165"/>
-      <c r="T21" s="165"/>
-      <c r="U21" s="165"/>
+      <c r="Q21" s="122"/>
+      <c r="R21" s="164"/>
+      <c r="S21" s="164"/>
+      <c r="T21" s="164"/>
+      <c r="U21" s="164"/>
     </row>
     <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="64">
+      <c r="A22" s="63">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="73">
+      <c r="C22" s="64"/>
+      <c r="D22" s="72">
         <v>2.61</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="74">
         <v>129616.17</v>
       </c>
-      <c r="F22" s="75">
-        <v>0</v>
-      </c>
-      <c r="G22" s="76">
+      <c r="F22" s="74">
+        <v>0</v>
+      </c>
+      <c r="G22" s="75">
         <f t="shared" si="0"/>
         <v>129616.17</v>
       </c>
-      <c r="H22" s="76">
+      <c r="H22" s="75">
         <f t="shared" si="2"/>
         <v>3888.4850999999999</v>
       </c>
-      <c r="I22" s="77">
-        <v>0</v>
-      </c>
-      <c r="J22" s="78">
+      <c r="I22" s="76">
+        <v>0</v>
+      </c>
+      <c r="J22" s="77">
         <f t="shared" si="3"/>
-        <v>127368.24455700001</v>
-      </c>
-      <c r="K22" s="159"/>
-      <c r="L22" s="159">
+        <v>145638.244557</v>
+      </c>
+      <c r="K22" s="158"/>
+      <c r="L22" s="158">
         <f t="shared" si="1"/>
         <v>2248.1120159999996</v>
       </c>
-      <c r="M22" s="80">
+      <c r="M22" s="79">
         <f t="shared" si="4"/>
-        <v>263121.17</v>
-      </c>
-      <c r="N22" s="81">
+        <v>281391.17</v>
+      </c>
+      <c r="N22" s="80">
         <f t="shared" si="5"/>
-        <v>278908.17</v>
-      </c>
-      <c r="O22" s="82">
+        <v>298275.17</v>
+      </c>
+      <c r="O22" s="81">
         <f t="shared" si="6"/>
-        <v>271015.17</v>
-      </c>
-      <c r="P22" s="43">
+        <v>289833.17</v>
+      </c>
+      <c r="P22" s="42">
         <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
-      <c r="Q22" s="123" t="s">
+      <c r="Q22" s="122" t="s">
         <v>98</v>
       </c>
-      <c r="R22" s="165"/>
-      <c r="S22" s="165"/>
-      <c r="T22" s="165"/>
-      <c r="U22" s="165"/>
+      <c r="R22" s="164"/>
+      <c r="S22" s="164"/>
+      <c r="T22" s="164"/>
+      <c r="U22" s="164"/>
     </row>
     <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="64">
+      <c r="A23" s="63">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="128"/>
-      <c r="D23" s="73">
+      <c r="C23" s="127"/>
+      <c r="D23" s="72">
         <v>4.28</v>
       </c>
-      <c r="E23" s="74">
+      <c r="E23" s="73">
         <v>212551.18</v>
       </c>
-      <c r="F23" s="241">
+      <c r="F23" s="74">
         <f>E23+RESUMEN!D57</f>
         <v>272551.18</v>
       </c>
-      <c r="G23" s="76">
+      <c r="G23" s="75">
         <f t="shared" si="0"/>
         <v>-60000</v>
       </c>
-      <c r="H23" s="76">
+      <c r="H23" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I23" s="77">
-        <v>0</v>
-      </c>
-      <c r="J23" s="78">
+      <c r="I23" s="76">
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
         <f t="shared" si="3"/>
-        <v>208864.40103600005</v>
-      </c>
-      <c r="K23" s="159"/>
-      <c r="L23" s="159">
+        <v>238824.40103600002</v>
+      </c>
+      <c r="K23" s="158"/>
+      <c r="L23" s="158">
         <f t="shared" si="1"/>
         <v>3686.5591680000002</v>
       </c>
-      <c r="M23" s="80">
+      <c r="M23" s="79">
         <f t="shared" si="4"/>
-        <v>152551.18</v>
-      </c>
-      <c r="N23" s="81">
+        <v>182511.18</v>
+      </c>
+      <c r="N23" s="80">
         <f t="shared" si="5"/>
-        <v>161704.18</v>
-      </c>
-      <c r="O23" s="82">
+        <v>193462.18</v>
+      </c>
+      <c r="O23" s="81">
         <f t="shared" si="6"/>
-        <v>157128.18</v>
-      </c>
-      <c r="P23" s="43">
+        <v>187986.18</v>
+      </c>
+      <c r="P23" s="42">
         <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="Q23" s="165"/>
-      <c r="R23" s="165"/>
-      <c r="S23" s="165"/>
-      <c r="T23" s="165"/>
-      <c r="U23" s="165"/>
+      <c r="Q23" s="164"/>
+      <c r="R23" s="164"/>
+      <c r="S23" s="164"/>
+      <c r="T23" s="164"/>
+      <c r="U23" s="164"/>
     </row>
     <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="64"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="189"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="159"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="81"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="43">
+      <c r="A24" s="63"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="188"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="158"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="42">
         <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="83"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="88"/>
-      <c r="K25" s="178"/>
-      <c r="L25" s="89"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="43"/>
+      <c r="A25" s="82"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="177"/>
+      <c r="L25" s="88"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="81"/>
+      <c r="P25" s="42"/>
     </row>
     <row r="26" spans="1:21" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="83"/>
-      <c r="B26" s="66"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="178"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="43"/>
+      <c r="A26" s="82"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="177"/>
+      <c r="L26" s="88"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="81"/>
+      <c r="P26" s="42"/>
     </row>
     <row r="27" spans="1:21" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="84"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="178"/>
-      <c r="L27" s="89"/>
-      <c r="M27" s="80"/>
-      <c r="N27" s="81"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="43"/>
+      <c r="A27" s="83"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="177"/>
+      <c r="L27" s="88"/>
+      <c r="M27" s="79"/>
+      <c r="N27" s="80"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="42"/>
     </row>
     <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="64"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="87"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="178"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="91"/>
-      <c r="N28" s="92"/>
-      <c r="O28" s="93"/>
-      <c r="P28" s="43"/>
+      <c r="A28" s="63"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="87"/>
+      <c r="K28" s="177"/>
+      <c r="L28" s="88"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="92"/>
+      <c r="P28" s="42"/>
     </row>
     <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="94"/>
-      <c r="B29" s="95"/>
-      <c r="C29" s="95"/>
-      <c r="D29" s="96">
+      <c r="A29" s="93"/>
+      <c r="B29" s="94"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="95">
         <f>SUM(D6:D28)</f>
         <v>100.08</v>
       </c>
-      <c r="E29" s="53">
+      <c r="E29" s="52">
         <f>SUM(E6:E28)</f>
         <v>9022054.7100000009</v>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="61">
         <f>SUM(F6:F28)</f>
         <v>4938034.42</v>
       </c>
-      <c r="G29" s="62">
+      <c r="G29" s="61">
         <f>SUM(G6:G28)</f>
         <v>4084020.29</v>
       </c>
-      <c r="H29" s="62">
-        <f t="shared" ref="H29:N29" si="10">SUM(H6:H28)</f>
+      <c r="H29" s="61">
+        <f t="shared" ref="H29:N29" si="11">SUM(H6:H28)</f>
         <v>131820.60869999998</v>
       </c>
-      <c r="I29" s="62">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="132">
-        <f t="shared" si="10"/>
-        <v>4883913.3774960004</v>
-      </c>
-      <c r="K29" s="132"/>
-      <c r="L29" s="62">
-        <f t="shared" si="10"/>
+      <c r="I29" s="61">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="131">
+        <f t="shared" si="11"/>
+        <v>5584473.3774959994</v>
+      </c>
+      <c r="K29" s="131"/>
+      <c r="L29" s="61">
+        <f t="shared" si="11"/>
         <v>86203.467647999991</v>
       </c>
-      <c r="M29" s="97">
+      <c r="M29" s="96">
         <f>SUM(M6:M23)</f>
-        <v>9309459.7100000009</v>
-      </c>
-      <c r="N29" s="97">
-        <f t="shared" si="10"/>
-        <v>9868029.7100000009</v>
-      </c>
-      <c r="O29" s="97">
+        <v>10010019.710000001</v>
+      </c>
+      <c r="N29" s="96">
+        <f t="shared" si="11"/>
+        <v>10610624.710000001</v>
+      </c>
+      <c r="O29" s="96">
         <f>SUM(O6:O28)</f>
-        <v>9588744.7100000009</v>
+        <v>10310320.710000001</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
     </row>
     <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="206" t="str">
+      <c r="B32" s="209" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="206"/>
-      <c r="D32" s="206"/>
-      <c r="E32" s="206"/>
-      <c r="F32" s="206"/>
-      <c r="G32" s="206"/>
-      <c r="H32" s="206"/>
-      <c r="I32" s="206"/>
-      <c r="J32" s="206"/>
-      <c r="K32" s="206"/>
-      <c r="L32" s="206"/>
-      <c r="M32" s="206"/>
+      <c r="C32" s="209"/>
+      <c r="D32" s="209"/>
+      <c r="E32" s="209"/>
+      <c r="F32" s="209"/>
+      <c r="G32" s="209"/>
+      <c r="H32" s="209"/>
+      <c r="I32" s="209"/>
+      <c r="J32" s="209"/>
+      <c r="K32" s="209"/>
+      <c r="L32" s="209"/>
+      <c r="M32" s="209"/>
     </row>
     <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="206"/>
-      <c r="C33" s="206"/>
-      <c r="D33" s="206"/>
-      <c r="E33" s="206"/>
-      <c r="F33" s="206"/>
-      <c r="G33" s="206"/>
-      <c r="H33" s="206"/>
-      <c r="I33" s="206"/>
-      <c r="J33" s="206"/>
-      <c r="K33" s="206"/>
-      <c r="L33" s="206"/>
-      <c r="M33" s="206"/>
+      <c r="B33" s="209"/>
+      <c r="C33" s="209"/>
+      <c r="D33" s="209"/>
+      <c r="E33" s="209"/>
+      <c r="F33" s="209"/>
+      <c r="G33" s="209"/>
+      <c r="H33" s="209"/>
+      <c r="I33" s="209"/>
+      <c r="J33" s="209"/>
+      <c r="K33" s="209"/>
+      <c r="L33" s="209"/>
+      <c r="M33" s="209"/>
     </row>
     <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="206"/>
-      <c r="C34" s="206"/>
-      <c r="D34" s="206"/>
-      <c r="E34" s="206"/>
-      <c r="F34" s="206"/>
-      <c r="G34" s="206"/>
-      <c r="H34" s="206"/>
-      <c r="I34" s="206"/>
-      <c r="J34" s="206"/>
-      <c r="K34" s="206"/>
-      <c r="L34" s="206"/>
-      <c r="M34" s="206"/>
+      <c r="B34" s="209"/>
+      <c r="C34" s="209"/>
+      <c r="D34" s="209"/>
+      <c r="E34" s="209"/>
+      <c r="F34" s="209"/>
+      <c r="G34" s="209"/>
+      <c r="H34" s="209"/>
+      <c r="I34" s="209"/>
+      <c r="J34" s="209"/>
+      <c r="K34" s="209"/>
+      <c r="L34" s="209"/>
+      <c r="M34" s="209"/>
     </row>
     <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="206"/>
-      <c r="C35" s="206"/>
-      <c r="D35" s="206"/>
-      <c r="E35" s="206"/>
-      <c r="F35" s="206"/>
-      <c r="G35" s="206"/>
-      <c r="H35" s="206"/>
-      <c r="I35" s="206"/>
-      <c r="J35" s="206"/>
-      <c r="K35" s="206"/>
-      <c r="L35" s="206"/>
-      <c r="M35" s="206"/>
+      <c r="B35" s="209"/>
+      <c r="C35" s="209"/>
+      <c r="D35" s="209"/>
+      <c r="E35" s="209"/>
+      <c r="F35" s="209"/>
+      <c r="G35" s="209"/>
+      <c r="H35" s="209"/>
+      <c r="I35" s="209"/>
+      <c r="J35" s="209"/>
+      <c r="K35" s="209"/>
+      <c r="L35" s="209"/>
+      <c r="M35" s="209"/>
     </row>
     <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="206"/>
-      <c r="C36" s="206"/>
-      <c r="D36" s="206"/>
-      <c r="E36" s="206"/>
-      <c r="F36" s="206"/>
-      <c r="G36" s="206"/>
-      <c r="H36" s="206"/>
-      <c r="I36" s="206"/>
-      <c r="J36" s="206"/>
-      <c r="K36" s="206"/>
-      <c r="L36" s="206"/>
-      <c r="M36" s="206"/>
+      <c r="B36" s="209"/>
+      <c r="C36" s="209"/>
+      <c r="D36" s="209"/>
+      <c r="E36" s="209"/>
+      <c r="F36" s="209"/>
+      <c r="G36" s="209"/>
+      <c r="H36" s="209"/>
+      <c r="I36" s="209"/>
+      <c r="J36" s="209"/>
+      <c r="K36" s="209"/>
+      <c r="L36" s="209"/>
+      <c r="M36" s="209"/>
     </row>
     <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="206"/>
-      <c r="C37" s="206"/>
-      <c r="D37" s="206"/>
-      <c r="E37" s="206"/>
-      <c r="F37" s="206"/>
-      <c r="G37" s="206"/>
-      <c r="H37" s="206"/>
-      <c r="I37" s="206"/>
-      <c r="J37" s="206"/>
-      <c r="K37" s="206"/>
-      <c r="L37" s="206"/>
-      <c r="M37" s="206"/>
+      <c r="B37" s="209"/>
+      <c r="C37" s="209"/>
+      <c r="D37" s="209"/>
+      <c r="E37" s="209"/>
+      <c r="F37" s="209"/>
+      <c r="G37" s="209"/>
+      <c r="H37" s="209"/>
+      <c r="I37" s="209"/>
+      <c r="J37" s="209"/>
+      <c r="K37" s="209"/>
+      <c r="L37" s="209"/>
+      <c r="M37" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -4476,138 +4469,138 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="169" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="171">
+      <c r="C2" s="170">
         <v>1</v>
       </c>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
-      <c r="F2" s="168"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="167"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="171" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="173" t="s">
+      <c r="C3" s="172" t="s">
         <v>105</v>
       </c>
-      <c r="F3" s="169"/>
+      <c r="F3" s="168"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="233"/>
+      <c r="C4" s="235"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="236"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="236"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="123"/>
-      <c r="B6" s="231"/>
-      <c r="C6" s="232"/>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="233"/>
-      <c r="N6" s="123"/>
-      <c r="O6" s="123"/>
+      <c r="A6" s="122"/>
+      <c r="B6" s="234"/>
+      <c r="C6" s="235"/>
+      <c r="D6" s="235"/>
+      <c r="E6" s="235"/>
+      <c r="F6" s="236"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="122"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="123"/>
-      <c r="B7" s="231"/>
-      <c r="C7" s="232"/>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="233"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="123"/>
+      <c r="A7" s="122"/>
+      <c r="B7" s="234"/>
+      <c r="C7" s="235"/>
+      <c r="D7" s="235"/>
+      <c r="E7" s="235"/>
+      <c r="F7" s="236"/>
+      <c r="N7" s="122"/>
+      <c r="O7" s="122"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="123"/>
-      <c r="B8" s="234"/>
-      <c r="C8" s="235"/>
-      <c r="D8" s="235"/>
-      <c r="E8" s="235"/>
-      <c r="F8" s="236"/>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
+      <c r="A8" s="122"/>
+      <c r="B8" s="237"/>
+      <c r="C8" s="238"/>
+      <c r="D8" s="238"/>
+      <c r="E8" s="238"/>
+      <c r="F8" s="239"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="122"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="123"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="123"/>
+      <c r="A9" s="122"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="122"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="123"/>
-      <c r="B10" s="174" t="s">
+      <c r="A10" s="122"/>
+      <c r="B10" s="173" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="175">
+      <c r="C10" s="174">
         <v>1</v>
       </c>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="168"/>
-      <c r="N10" s="123"/>
-      <c r="O10" s="123"/>
+      <c r="D10" s="166"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="167"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="122"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="123"/>
-      <c r="B11" s="176" t="s">
+      <c r="A11" s="122"/>
+      <c r="B11" s="175" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="177" t="s">
+      <c r="C11" s="176" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="169"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123"/>
+      <c r="F11" s="168"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="122"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="231" t="s">
+      <c r="B12" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="232"/>
-      <c r="D12" s="232"/>
-      <c r="E12" s="232"/>
-      <c r="F12" s="233"/>
+      <c r="C12" s="235"/>
+      <c r="D12" s="235"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="236"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="231"/>
-      <c r="C13" s="232"/>
-      <c r="D13" s="232"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="233"/>
+      <c r="B13" s="234"/>
+      <c r="C13" s="235"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="236"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="231"/>
-      <c r="C14" s="232"/>
-      <c r="D14" s="232"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="233"/>
+      <c r="B14" s="234"/>
+      <c r="C14" s="235"/>
+      <c r="D14" s="235"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="236"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="231"/>
-      <c r="C15" s="232"/>
-      <c r="D15" s="232"/>
-      <c r="E15" s="232"/>
-      <c r="F15" s="233"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="235"/>
+      <c r="D15" s="235"/>
+      <c r="E15" s="235"/>
+      <c r="F15" s="236"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="234"/>
-      <c r="C16" s="235"/>
-      <c r="D16" s="235"/>
-      <c r="E16" s="235"/>
-      <c r="F16" s="236"/>
+      <c r="B16" s="237"/>
+      <c r="C16" s="238"/>
+      <c r="D16" s="238"/>
+      <c r="E16" s="238"/>
+      <c r="F16" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="2">
